--- a/resources/data-imports/Monsters/purgatory-monsters.xlsx
+++ b/resources/data-imports/Monsters/purgatory-monsters.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -548,6 +548,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -607,12 +608,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -636,37 +641,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -740,6879 +745,6879 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX60"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="0" width="11.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="8.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="5.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="0" width="21.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="16.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="14.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="20.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="24.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="14.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="14.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="16.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="17.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="21.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="12.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="13.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="14.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="11.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="0" width="21.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="20.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="19.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="4" style="1" width="11.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="8.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="9.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="5.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="11.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="1" width="21.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="14.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="20.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="24.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="14.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="14.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="21.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="12.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="13.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="14.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="11.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="21.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="20.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="19.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="0" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="0" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="0" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="0" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="0" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="0" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="0" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="0" t="s">
+      <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="0" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="0" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="0" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="0" t="s">
+      <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="0" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="0" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="0" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="0" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="0" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="0" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="0" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="0" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="0" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="0" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="0" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="0" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="0" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="0" t="s">
+      <c r="AR1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="0" t="s">
+      <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="0" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="0" t="s">
+      <c r="AU1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="0" t="s">
+      <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="0" t="s">
+      <c r="AW1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="0" t="s">
+      <c r="AX1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.3562832</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.3562832</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.3562832</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.3562832</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S2" s="0" t="n">
+      <c r="S2" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="1" t="n">
+      <c r="U2" s="2" t="n">
         <v>51.9895</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.2546985</v>
       </c>
-      <c r="W2" s="1" t="n">
-        <v>366136186.5</v>
-      </c>
-      <c r="X2" s="0" t="n">
+      <c r="W2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="X2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" s="0" t="s">
+      <c r="Y2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="0" t="n">
+      <c r="AA2" s="1" t="n">
         <v>106451900</v>
       </c>
-      <c r="AB2" s="0" t="n">
+      <c r="AB2" s="1" t="n">
         <v>106451900</v>
       </c>
       <c r="AC2" s="0" t="n">
-        <v>0.2559435</v>
+        <v>0.001</v>
       </c>
       <c r="AD2" s="0" t="n">
-        <v>0.2559435</v>
+        <v>0.001</v>
       </c>
       <c r="AE2" s="0" t="n">
-        <v>0.2559435</v>
+        <v>0.001</v>
       </c>
       <c r="AF2" s="0" t="n">
-        <v>0.2559435</v>
+        <v>0.001</v>
       </c>
       <c r="AG2" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AH2" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AI2" s="1" t="n">
         <v>0.2546985</v>
       </c>
-      <c r="AH2" s="0" t="n">
+      <c r="AJ2" s="1" t="n">
         <v>0.2546985</v>
       </c>
-      <c r="AI2" s="0" t="n">
+      <c r="AK2" s="1" t="n">
         <v>0.2546985</v>
       </c>
-      <c r="AJ2" s="0" t="n">
+      <c r="AL2" s="1" t="n">
         <v>0.2546985</v>
       </c>
-      <c r="AK2" s="0" t="n">
-        <v>0.2546985</v>
-      </c>
-      <c r="AL2" s="0" t="n">
-        <v>0.2546985</v>
-      </c>
-      <c r="AO2" s="0" t="s">
+      <c r="AO2" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW2" s="0" t="n">
-        <v>0.2546985</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.3626791960064</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.3626791960064</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.3626791960064</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.3626791960064</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U3" s="1" t="n">
+      <c r="U3" s="2" t="n">
         <v>54.058162205</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.259485303609</v>
       </c>
-      <c r="W3" s="1" t="n">
-        <v>383016305.899322</v>
-      </c>
-      <c r="X3" s="0" t="n">
+      <c r="W3" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA3" s="1" t="n">
+      <c r="AA3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
-      <c r="AB3" s="1" t="n">
+      <c r="AB3" s="2" t="n">
         <v>113320070.1361</v>
       </c>
       <c r="AC3" s="0" t="n">
-        <v>0.262028300769</v>
+        <v>0.001121</v>
       </c>
       <c r="AD3" s="0" t="n">
-        <v>0.262028300769</v>
+        <v>0.001121</v>
       </c>
       <c r="AE3" s="0" t="n">
-        <v>0.262028300769</v>
+        <v>0.001121</v>
       </c>
       <c r="AF3" s="0" t="n">
-        <v>0.262028300769</v>
+        <v>0.001121</v>
       </c>
       <c r="AG3" s="0" t="n">
+        <v>0.001121</v>
+      </c>
+      <c r="AH3" s="0" t="n">
+        <v>0.001121</v>
+      </c>
+      <c r="AI3" s="1" t="n">
         <v>0.259485303609</v>
       </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>0.259485303609</v>
       </c>
-      <c r="AI3" s="0" t="n">
+      <c r="AK3" s="1" t="n">
         <v>0.259485303609</v>
       </c>
-      <c r="AJ3" s="0" t="n">
+      <c r="AL3" s="1" t="n">
         <v>0.259485303609</v>
       </c>
-      <c r="AK3" s="0" t="n">
-        <v>0.259485303609</v>
-      </c>
-      <c r="AL3" s="0" t="n">
-        <v>0.259485303609</v>
-      </c>
-      <c r="AO3" s="0" t="s">
+      <c r="AO3" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW3" s="0" t="n">
-        <v>0.259485303609</v>
+        <v>0.001121</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.369190012933107</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.369190012933107</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.369190012933107</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.369190012933107</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="U4" s="2" t="n">
         <v>56.2091364791369</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.264362070405028</v>
       </c>
-      <c r="W4" s="1" t="n">
-        <v>400674656.026558</v>
-      </c>
-      <c r="X4" s="0" t="n">
+      <c r="W4" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="X4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Z4" s="0" t="s">
+      <c r="Z4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AA4" s="1" t="n">
+      <c r="AA4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
-      <c r="AB4" s="1" t="n">
+      <c r="AB4" s="2" t="n">
         <v>120631367.741211</v>
       </c>
       <c r="AC4" s="0" t="n">
-        <v>0.268257761591482</v>
+        <v>0.001256</v>
       </c>
       <c r="AD4" s="0" t="n">
-        <v>0.268257761591482</v>
+        <v>0.001256</v>
       </c>
       <c r="AE4" s="0" t="n">
-        <v>0.268257761591482</v>
+        <v>0.001256</v>
       </c>
       <c r="AF4" s="0" t="n">
-        <v>0.268257761591482</v>
+        <v>0.001256</v>
       </c>
       <c r="AG4" s="0" t="n">
+        <v>0.001256</v>
+      </c>
+      <c r="AH4" s="0" t="n">
+        <v>0.001256</v>
+      </c>
+      <c r="AI4" s="1" t="n">
         <v>0.264362070405028</v>
       </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>0.264362070405028</v>
       </c>
-      <c r="AI4" s="0" t="n">
+      <c r="AK4" s="1" t="n">
         <v>0.264362070405028</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AL4" s="1" t="n">
         <v>0.264362070405028</v>
       </c>
-      <c r="AK4" s="0" t="n">
-        <v>0.264362070405028</v>
-      </c>
-      <c r="AL4" s="0" t="n">
-        <v>0.264362070405028</v>
-      </c>
-      <c r="AO4" s="0" t="s">
+      <c r="AO4" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW4" s="0" t="n">
-        <v>0.264362070405028</v>
+        <v>0.001256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="I5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.375817712045282</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.375817712045282</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.375817712045282</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.375817712045282</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="U5" s="2" t="n">
         <v>58.4456980196418</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.26933049115622</v>
       </c>
-      <c r="W5" s="1" t="n">
-        <v>419147115.956466</v>
-      </c>
-      <c r="X5" s="0" t="n">
+      <c r="W5" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="X5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AA5" s="1" t="n">
+      <c r="AA5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
-      <c r="AB5" s="1" t="n">
+      <c r="AB5" s="2" t="n">
         <v>128414382.956506</v>
       </c>
       <c r="AC5" s="0" t="n">
-        <v>0.274635321615558</v>
+        <v>0.001408</v>
       </c>
       <c r="AD5" s="0" t="n">
-        <v>0.274635321615558</v>
+        <v>0.001408</v>
       </c>
       <c r="AE5" s="0" t="n">
-        <v>0.274635321615558</v>
+        <v>0.001408</v>
       </c>
       <c r="AF5" s="0" t="n">
-        <v>0.274635321615558</v>
+        <v>0.001408</v>
       </c>
       <c r="AG5" s="0" t="n">
+        <v>0.001408</v>
+      </c>
+      <c r="AH5" s="0" t="n">
+        <v>0.001408</v>
+      </c>
+      <c r="AI5" s="1" t="n">
         <v>0.26933049115622</v>
       </c>
-      <c r="AH5" s="0" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>0.26933049115622</v>
       </c>
-      <c r="AI5" s="0" t="n">
+      <c r="AK5" s="1" t="n">
         <v>0.26933049115622</v>
       </c>
-      <c r="AJ5" s="0" t="n">
+      <c r="AL5" s="1" t="n">
         <v>0.26933049115622</v>
       </c>
-      <c r="AK5" s="0" t="n">
-        <v>0.26933049115622</v>
-      </c>
-      <c r="AL5" s="0" t="n">
-        <v>0.26933049115622</v>
-      </c>
-      <c r="AO5" s="0" t="s">
+      <c r="AO5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW5" s="0" t="n">
-        <v>0.26933049115622</v>
+        <v>0.001408</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>151</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="I6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.382564391611919</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.382564391611919</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.382564391611919</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.382564391611919</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="U6" s="2" t="n">
         <v>60.7712523438434</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.27439228840701</v>
       </c>
-      <c r="W6" s="1" t="n">
-        <v>438471218.910783</v>
-      </c>
-      <c r="X6" s="0" t="n">
+      <c r="W6" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="X6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Z6" s="0" t="s">
+      <c r="Z6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AA6" s="1" t="n">
+      <c r="AA6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
-      <c r="AB6" s="1" t="n">
+      <c r="AB6" s="2" t="n">
         <v>136699550.530477</v>
       </c>
       <c r="AC6" s="0" t="n">
-        <v>0.281164501751646</v>
+        <v>0.001579</v>
       </c>
       <c r="AD6" s="0" t="n">
-        <v>0.281164501751646</v>
+        <v>0.001579</v>
       </c>
       <c r="AE6" s="0" t="n">
-        <v>0.281164501751646</v>
+        <v>0.001579</v>
       </c>
       <c r="AF6" s="0" t="n">
-        <v>0.281164501751646</v>
+        <v>0.001579</v>
       </c>
       <c r="AG6" s="0" t="n">
+        <v>0.001579</v>
+      </c>
+      <c r="AH6" s="0" t="n">
+        <v>0.001579</v>
+      </c>
+      <c r="AI6" s="1" t="n">
         <v>0.27439228840701</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>0.27439228840701</v>
       </c>
-      <c r="AI6" s="0" t="n">
+      <c r="AK6" s="1" t="n">
         <v>0.27439228840701</v>
       </c>
-      <c r="AJ6" s="0" t="n">
+      <c r="AL6" s="1" t="n">
         <v>0.27439228840701</v>
       </c>
-      <c r="AK6" s="0" t="n">
-        <v>0.27439228840701</v>
-      </c>
-      <c r="AL6" s="0" t="n">
-        <v>0.27439228840701</v>
-      </c>
-      <c r="AO6" s="0" t="s">
+      <c r="AO6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW6" s="0" t="n">
-        <v>0.27439228840701</v>
+        <v>0.001579</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="F7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="I7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.389432187570136</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.389432187570136</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.389432187570136</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.389432187570136</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="U7" s="2" t="n">
         <v>63.1893404746049</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.279549217075331</v>
       </c>
-      <c r="W7" s="1" t="n">
-        <v>458686228.520002</v>
-      </c>
-      <c r="X7" s="0" t="n">
+      <c r="W7" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="X7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AA7" s="1" t="n">
+      <c r="AA7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
-      <c r="AB7" s="1" t="n">
+      <c r="AB7" s="2" t="n">
         <v>145519268.831153</v>
       </c>
       <c r="AC7" s="0" t="n">
-        <v>0.28784890661629</v>
+        <v>0.001769</v>
       </c>
       <c r="AD7" s="0" t="n">
-        <v>0.28784890661629</v>
+        <v>0.001769</v>
       </c>
       <c r="AE7" s="0" t="n">
-        <v>0.28784890661629</v>
+        <v>0.001769</v>
       </c>
       <c r="AF7" s="0" t="n">
-        <v>0.28784890661629</v>
+        <v>0.001769</v>
       </c>
       <c r="AG7" s="0" t="n">
+        <v>0.001769</v>
+      </c>
+      <c r="AH7" s="0" t="n">
+        <v>0.001769</v>
+      </c>
+      <c r="AI7" s="1" t="n">
         <v>0.279549217075331</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>0.279549217075331</v>
       </c>
-      <c r="AI7" s="0" t="n">
+      <c r="AK7" s="1" t="n">
         <v>0.279549217075331</v>
       </c>
-      <c r="AJ7" s="0" t="n">
+      <c r="AL7" s="1" t="n">
         <v>0.279549217075331</v>
       </c>
-      <c r="AK7" s="0" t="n">
-        <v>0.279549217075331</v>
-      </c>
-      <c r="AL7" s="0" t="n">
-        <v>0.279549217075331</v>
-      </c>
-      <c r="AM7" s="0" t="s">
+      <c r="AM7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AN7" s="0" t="n">
+      <c r="AN7" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="AO7" s="0" t="s">
+      <c r="AO7" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW7" s="0" t="n">
-        <v>0.279549217075331</v>
+        <v>0.001769</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>153</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="I8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.396423274201395</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.396423274201395</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.396423274201395</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.396423274201395</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U8" s="1" t="n">
+      <c r="U8" s="2" t="n">
         <v>65.7036443320894</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>0.284803065061045</v>
       </c>
-      <c r="W8" s="1" t="n">
-        <v>479833218.601089</v>
-      </c>
-      <c r="X8" s="0" t="n">
+      <c r="W8" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="X8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Z8" s="0" t="s">
+      <c r="Z8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AA8" s="1" t="n">
+      <c r="AA8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
-      <c r="AB8" s="1" t="n">
+      <c r="AB8" s="2" t="n">
         <v>154908026.53687</v>
       </c>
       <c r="AC8" s="0" t="n">
-        <v>0.294692226522186</v>
+        <v>0.001983</v>
       </c>
       <c r="AD8" s="0" t="n">
-        <v>0.294692226522186</v>
+        <v>0.001983</v>
       </c>
       <c r="AE8" s="0" t="n">
-        <v>0.294692226522186</v>
+        <v>0.001983</v>
       </c>
       <c r="AF8" s="0" t="n">
-        <v>0.294692226522186</v>
+        <v>0.001983</v>
       </c>
       <c r="AG8" s="0" t="n">
+        <v>0.001983</v>
+      </c>
+      <c r="AH8" s="0" t="n">
+        <v>0.001983</v>
+      </c>
+      <c r="AI8" s="1" t="n">
         <v>0.284803065061045</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>0.284803065061045</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="AK8" s="1" t="n">
         <v>0.284803065061045</v>
       </c>
-      <c r="AJ8" s="0" t="n">
+      <c r="AL8" s="1" t="n">
         <v>0.284803065061045</v>
       </c>
-      <c r="AK8" s="0" t="n">
-        <v>0.284803065061045</v>
-      </c>
-      <c r="AL8" s="0" t="n">
-        <v>0.284803065061045</v>
-      </c>
-      <c r="AO8" s="0" t="s">
+      <c r="AO8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW8" s="0" t="n">
-        <v>0.284803065061045</v>
+        <v>0.001983</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.403539864819859</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.403539864819859</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.403539864819859</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.403539864819859</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="U9" s="2" t="n">
         <v>68.3179923400633</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <v>0.290155653865802</v>
       </c>
-      <c r="W9" s="1" t="n">
-        <v>501955156.61321</v>
-      </c>
-      <c r="X9" s="0" t="n">
+      <c r="W9" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="X9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Z9" s="0" t="s">
+      <c r="Z9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AA9" s="1" t="n">
+      <c r="AA9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
-      <c r="AB9" s="1" t="n">
+      <c r="AB9" s="2" t="n">
         <v>164902537.501002</v>
       </c>
       <c r="AC9" s="0" t="n">
-        <v>0.301698239515524</v>
+        <v>0.002223</v>
       </c>
       <c r="AD9" s="0" t="n">
-        <v>0.301698239515524</v>
+        <v>0.002223</v>
       </c>
       <c r="AE9" s="0" t="n">
-        <v>0.301698239515524</v>
+        <v>0.002223</v>
       </c>
       <c r="AF9" s="0" t="n">
-        <v>0.301698239515524</v>
+        <v>0.002223</v>
       </c>
       <c r="AG9" s="0" t="n">
+        <v>0.002223</v>
+      </c>
+      <c r="AH9" s="0" t="n">
+        <v>0.002223</v>
+      </c>
+      <c r="AI9" s="1" t="n">
         <v>0.290155653865802</v>
       </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>0.290155653865802</v>
       </c>
-      <c r="AI9" s="0" t="n">
+      <c r="AK9" s="1" t="n">
         <v>0.290155653865802</v>
       </c>
-      <c r="AJ9" s="0" t="n">
+      <c r="AL9" s="1" t="n">
         <v>0.290155653865802</v>
       </c>
-      <c r="AK9" s="0" t="n">
-        <v>0.290155653865802</v>
-      </c>
-      <c r="AL9" s="0" t="n">
-        <v>0.290155653865802</v>
-      </c>
-      <c r="AO9" s="0" t="s">
+      <c r="AO9" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW9" s="0" t="n">
-        <v>0.290155653865802</v>
+        <v>0.002223</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.410784212473105</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.410784212473105</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.410784212473105</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.410784212473105</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="S10" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="U10" s="2" t="n">
         <v>71.0363652552744</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.295608839224556</v>
       </c>
-      <c r="W10" s="1" t="n">
-        <v>525096990.96106</v>
-      </c>
-      <c r="X10" s="0" t="n">
+      <c r="W10" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="X10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="0" t="s">
+      <c r="Y10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Z10" s="0" t="s">
+      <c r="Z10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AA10" s="1" t="n">
+      <c r="AA10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
-      <c r="AB10" s="1" t="n">
+      <c r="AB10" s="2" t="n">
         <v>175541884.31803</v>
       </c>
       <c r="AC10" s="0" t="n">
-        <v>0.308870813461766</v>
+        <v>0.002492</v>
       </c>
       <c r="AD10" s="0" t="n">
-        <v>0.308870813461766</v>
+        <v>0.002492</v>
       </c>
       <c r="AE10" s="0" t="n">
-        <v>0.308870813461766</v>
+        <v>0.002492</v>
       </c>
       <c r="AF10" s="0" t="n">
-        <v>0.308870813461766</v>
+        <v>0.002492</v>
       </c>
       <c r="AG10" s="0" t="n">
+        <v>0.002492</v>
+      </c>
+      <c r="AH10" s="0" t="n">
+        <v>0.002492</v>
+      </c>
+      <c r="AI10" s="1" t="n">
         <v>0.295608839224556</v>
       </c>
-      <c r="AH10" s="0" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>0.295608839224556</v>
       </c>
-      <c r="AI10" s="0" t="n">
+      <c r="AK10" s="1" t="n">
         <v>0.295608839224556</v>
       </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AL10" s="1" t="n">
         <v>0.295608839224556</v>
       </c>
-      <c r="AK10" s="0" t="n">
-        <v>0.295608839224556</v>
-      </c>
-      <c r="AL10" s="0" t="n">
-        <v>0.295608839224556</v>
-      </c>
-      <c r="AO10" s="0" t="s">
+      <c r="AO10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW10" s="0" t="n">
-        <v>0.295608839224556</v>
+        <v>0.002492</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.418158610655422</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.418158610655422</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.418158610655422</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.418158610655422</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="U11" s="2" t="n">
         <v>73.8629022287817</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.301164511748942</v>
       </c>
-      <c r="W11" s="1" t="n">
-        <v>549305742.323164</v>
-      </c>
-      <c r="X11" s="0" t="n">
+      <c r="W11" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="X11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y11" s="0" t="s">
+      <c r="Y11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z11" s="0" t="s">
+      <c r="Z11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AA11" s="1" t="n">
+      <c r="AA11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
-      <c r="AB11" s="1" t="n">
+      <c r="AB11" s="2" t="n">
         <v>186867671.152345</v>
       </c>
       <c r="AC11" s="0" t="n">
-        <v>0.316213908181006</v>
+        <v>0.002793</v>
       </c>
       <c r="AD11" s="0" t="n">
-        <v>0.316213908181006</v>
+        <v>0.002793</v>
       </c>
       <c r="AE11" s="0" t="n">
-        <v>0.316213908181006</v>
+        <v>0.002793</v>
       </c>
       <c r="AF11" s="0" t="n">
-        <v>0.316213908181006</v>
+        <v>0.002793</v>
       </c>
       <c r="AG11" s="0" t="n">
+        <v>0.002793</v>
+      </c>
+      <c r="AH11" s="0" t="n">
+        <v>0.002793</v>
+      </c>
+      <c r="AI11" s="1" t="n">
         <v>0.301164511748942</v>
       </c>
-      <c r="AH11" s="0" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>0.301164511748942</v>
       </c>
-      <c r="AI11" s="0" t="n">
+      <c r="AK11" s="1" t="n">
         <v>0.301164511748942</v>
       </c>
-      <c r="AJ11" s="0" t="n">
+      <c r="AL11" s="1" t="n">
         <v>0.301164511748942</v>
       </c>
-      <c r="AK11" s="0" t="n">
-        <v>0.301164511748942</v>
-      </c>
-      <c r="AL11" s="0" t="n">
-        <v>0.301164511748942</v>
-      </c>
-      <c r="AO11" s="0" t="s">
+      <c r="AO11" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW11" s="0" t="n">
-        <v>0.301164511748942</v>
+        <v>0.002793</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="F12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>0.425665394033908</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.425665394033908</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.425665394033908</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.425665394033908</v>
       </c>
-      <c r="R12" s="0" t="n">
+      <c r="R12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S12" s="0" t="n">
+      <c r="S12" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T12" s="0" t="s">
+      <c r="T12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U12" s="1" t="n">
+      <c r="U12" s="2" t="n">
         <v>76.801907108465</v>
       </c>
-      <c r="V12" s="0" t="n">
+      <c r="V12" s="1" t="n">
         <v>0.306824597582752</v>
       </c>
-      <c r="W12" s="1" t="n">
-        <v>574630599.190729</v>
-      </c>
-      <c r="X12" s="0" t="n">
+      <c r="W12" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="X12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y12" s="0" t="s">
+      <c r="Y12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Z12" s="0" t="s">
+      <c r="Z12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AA12" s="1" t="n">
+      <c r="AA12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
-      <c r="AB12" s="1" t="n">
+      <c r="AB12" s="2" t="n">
         <v>198924186.427423</v>
       </c>
       <c r="AC12" s="0" t="n">
-        <v>0.323731577634101</v>
+        <v>0.003131</v>
       </c>
       <c r="AD12" s="0" t="n">
-        <v>0.323731577634101</v>
+        <v>0.003131</v>
       </c>
       <c r="AE12" s="0" t="n">
-        <v>0.323731577634101</v>
+        <v>0.003131</v>
       </c>
       <c r="AF12" s="0" t="n">
-        <v>0.323731577634101</v>
+        <v>0.003131</v>
       </c>
       <c r="AG12" s="0" t="n">
+        <v>0.003131</v>
+      </c>
+      <c r="AH12" s="0" t="n">
+        <v>0.003131</v>
+      </c>
+      <c r="AI12" s="1" t="n">
         <v>0.306824597582752</v>
       </c>
-      <c r="AH12" s="0" t="n">
+      <c r="AJ12" s="1" t="n">
         <v>0.306824597582752</v>
       </c>
-      <c r="AI12" s="0" t="n">
+      <c r="AK12" s="1" t="n">
         <v>0.306824597582752</v>
       </c>
-      <c r="AJ12" s="0" t="n">
+      <c r="AL12" s="1" t="n">
         <v>0.306824597582752</v>
       </c>
-      <c r="AK12" s="0" t="n">
-        <v>0.306824597582752</v>
-      </c>
-      <c r="AL12" s="0" t="n">
-        <v>0.306824597582752</v>
-      </c>
-      <c r="AO12" s="0" t="s">
+      <c r="AO12" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW12" s="0" t="n">
-        <v>0.306824597582752</v>
+        <v>0.003131</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>0.433306939187605</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <v>0.433306939187605</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.433306939187605</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>0.433306939187605</v>
       </c>
-      <c r="R13" s="0" t="n">
+      <c r="R13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S13" s="0" t="n">
+      <c r="S13" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T13" s="0" t="s">
+      <c r="T13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U13" s="1" t="n">
+      <c r="U13" s="2" t="n">
         <v>79.8578549923108</v>
       </c>
-      <c r="V13" s="0" t="n">
+      <c r="V13" s="1" t="n">
         <v>0.312591059069722</v>
       </c>
-      <c r="W13" s="1" t="n">
-        <v>601123017.811152</v>
-      </c>
-      <c r="X13" s="0" t="n">
+      <c r="W13" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="X13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y13" s="0" t="s">
+      <c r="Y13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Z13" s="0" t="s">
+      <c r="Z13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AA13" s="1" t="n">
+      <c r="AA13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
-      <c r="AB13" s="1" t="n">
+      <c r="AB13" s="2" t="n">
         <v>211758576.011533</v>
       </c>
       <c r="AC13" s="0" t="n">
-        <v>0.331427972160774</v>
+        <v>0.00351</v>
       </c>
       <c r="AD13" s="0" t="n">
-        <v>0.331427972160774</v>
+        <v>0.00351</v>
       </c>
       <c r="AE13" s="0" t="n">
-        <v>0.331427972160774</v>
+        <v>0.00351</v>
       </c>
       <c r="AF13" s="0" t="n">
-        <v>0.331427972160774</v>
+        <v>0.00351</v>
       </c>
       <c r="AG13" s="0" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="AH13" s="0" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="AI13" s="1" t="n">
         <v>0.312591059069722</v>
       </c>
-      <c r="AH13" s="0" t="n">
+      <c r="AJ13" s="1" t="n">
         <v>0.312591059069722</v>
       </c>
-      <c r="AI13" s="0" t="n">
+      <c r="AK13" s="1" t="n">
         <v>0.312591059069722</v>
       </c>
-      <c r="AJ13" s="0" t="n">
+      <c r="AL13" s="1" t="n">
         <v>0.312591059069722</v>
       </c>
-      <c r="AK13" s="0" t="n">
-        <v>0.312591059069722</v>
-      </c>
-      <c r="AL13" s="0" t="n">
-        <v>0.312591059069722</v>
-      </c>
-      <c r="AO13" s="0" t="s">
+      <c r="AO13" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW13" s="0" t="n">
-        <v>0.312591059069722</v>
+        <v>0.00351</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="I14" s="1" t="n">
+      <c r="I14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="1" t="n">
         <v>0.4410856653599</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <v>0.4410856653599</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <v>0.4410856653599</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <v>0.4410856653599</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S14" s="0" t="n">
+      <c r="S14" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T14" s="0" t="s">
+      <c r="T14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U14" s="1" t="n">
+      <c r="U14" s="2" t="n">
         <v>83.0353990424548</v>
       </c>
-      <c r="V14" s="0" t="n">
+      <c r="V14" s="1" t="n">
         <v>0.318465895433878</v>
       </c>
-      <c r="W14" s="1" t="n">
-        <v>628836826.739277</v>
-      </c>
-      <c r="X14" s="0" t="n">
+      <c r="W14" s="2" t="n">
+        <v>904</v>
+      </c>
+      <c r="X14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y14" s="0" t="s">
+      <c r="Y14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Z14" s="0" t="s">
+      <c r="Z14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AA14" s="1" t="n">
+      <c r="AA14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
-      <c r="AB14" s="1" t="n">
+      <c r="AB14" s="2" t="n">
         <v>225421027.577222</v>
       </c>
       <c r="AC14" s="0" t="n">
-        <v>0.339307340770925</v>
+        <v>0.003934</v>
       </c>
       <c r="AD14" s="0" t="n">
-        <v>0.339307340770925</v>
+        <v>0.003934</v>
       </c>
       <c r="AE14" s="0" t="n">
-        <v>0.339307340770925</v>
+        <v>0.003934</v>
       </c>
       <c r="AF14" s="0" t="n">
-        <v>0.339307340770925</v>
+        <v>0.003934</v>
       </c>
       <c r="AG14" s="0" t="n">
+        <v>0.003934</v>
+      </c>
+      <c r="AH14" s="0" t="n">
+        <v>0.003934</v>
+      </c>
+      <c r="AI14" s="1" t="n">
         <v>0.318465895433878</v>
       </c>
-      <c r="AH14" s="0" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>0.318465895433878</v>
       </c>
-      <c r="AI14" s="0" t="n">
+      <c r="AK14" s="1" t="n">
         <v>0.318465895433878</v>
       </c>
-      <c r="AJ14" s="0" t="n">
+      <c r="AL14" s="1" t="n">
         <v>0.318465895433878</v>
       </c>
-      <c r="AK14" s="0" t="n">
-        <v>0.318465895433878</v>
-      </c>
-      <c r="AL14" s="0" t="n">
-        <v>0.318465895433878</v>
-      </c>
-      <c r="AO14" s="0" t="s">
+      <c r="AO14" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW14" s="0" t="n">
-        <v>0.318465895433878</v>
+        <v>0.003934</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="I15" s="1" t="n">
+      <c r="I15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" s="1" t="n">
         <v>0.449004035224441</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="1" t="n">
         <v>0.449004035224441</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="1" t="n">
         <v>0.449004035224441</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <v>0.449004035224441</v>
       </c>
-      <c r="R15" s="0" t="n">
+      <c r="R15" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S15" s="0" t="n">
+      <c r="S15" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T15" s="0" t="s">
+      <c r="T15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="1" t="n">
+      <c r="U15" s="2" t="n">
         <v>86.3393775703541</v>
       </c>
-      <c r="V15" s="0" t="n">
+      <c r="V15" s="1" t="n">
         <v>0.324451143472663</v>
       </c>
-      <c r="W15" s="1" t="n">
-        <v>657828336.2088</v>
-      </c>
-      <c r="X15" s="0" t="n">
+      <c r="W15" s="2" t="n">
+        <v>1242</v>
+      </c>
+      <c r="X15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y15" s="0" t="s">
+      <c r="Y15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Z15" s="0" t="s">
+      <c r="Z15" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AA15" s="1" t="n">
+      <c r="AA15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
-      <c r="AB15" s="1" t="n">
+      <c r="AB15" s="2" t="n">
         <v>239964966.855476</v>
       </c>
       <c r="AC15" s="0" t="n">
-        <v>0.347374033490413</v>
+        <v>0.00441</v>
       </c>
       <c r="AD15" s="0" t="n">
-        <v>0.347374033490413</v>
+        <v>0.00441</v>
       </c>
       <c r="AE15" s="0" t="n">
-        <v>0.347374033490413</v>
+        <v>0.00441</v>
       </c>
       <c r="AF15" s="0" t="n">
-        <v>0.347374033490413</v>
+        <v>0.00441</v>
       </c>
       <c r="AG15" s="0" t="n">
+        <v>0.00441</v>
+      </c>
+      <c r="AH15" s="0" t="n">
+        <v>0.00441</v>
+      </c>
+      <c r="AI15" s="1" t="n">
         <v>0.324451143472663</v>
       </c>
-      <c r="AH15" s="0" t="n">
+      <c r="AJ15" s="1" t="n">
         <v>0.324451143472663</v>
       </c>
-      <c r="AI15" s="0" t="n">
+      <c r="AK15" s="1" t="n">
         <v>0.324451143472663</v>
       </c>
-      <c r="AJ15" s="0" t="n">
+      <c r="AL15" s="1" t="n">
         <v>0.324451143472663</v>
       </c>
-      <c r="AK15" s="0" t="n">
-        <v>0.324451143472663</v>
-      </c>
-      <c r="AL15" s="0" t="n">
-        <v>0.324451143472663</v>
-      </c>
-      <c r="AO15" s="0" t="s">
+      <c r="AO15" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW15" s="0" t="n">
-        <v>0.324451143472663</v>
+        <v>0.00441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="K16" s="1" t="n">
         <v>0.457064555664791</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="1" t="n">
         <v>0.457064555664791</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <v>0.457064555664791</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <v>0.457064555664791</v>
       </c>
-      <c r="R16" s="0" t="n">
+      <c r="R16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S16" s="0" t="n">
+      <c r="S16" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T16" s="0" t="s">
+      <c r="T16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U16" s="1" t="n">
+      <c r="U16" s="2" t="n">
         <v>89.7748214038785</v>
       </c>
-      <c r="V16" s="0" t="n">
+      <c r="V16" s="1" t="n">
         <v>0.330548878263088</v>
       </c>
-      <c r="W16" s="1" t="n">
-        <v>688156452.546086</v>
-      </c>
-      <c r="X16" s="0" t="n">
+      <c r="W16" s="2" t="n">
+        <v>1706</v>
+      </c>
+      <c r="X16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y16" s="0" t="s">
+      <c r="Y16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="Z16" s="0" t="s">
+      <c r="Z16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AA16" s="1" t="n">
+      <c r="AA16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
-      <c r="AB16" s="1" t="n">
+      <c r="AB16" s="2" t="n">
         <v>255447266.552025</v>
       </c>
       <c r="AC16" s="0" t="n">
-        <v>0.355632503762614</v>
+        <v>0.004943</v>
       </c>
       <c r="AD16" s="0" t="n">
-        <v>0.355632503762614</v>
+        <v>0.004943</v>
       </c>
       <c r="AE16" s="0" t="n">
-        <v>0.355632503762614</v>
+        <v>0.004943</v>
       </c>
       <c r="AF16" s="0" t="n">
-        <v>0.355632503762614</v>
+        <v>0.004943</v>
       </c>
       <c r="AG16" s="0" t="n">
+        <v>0.004943</v>
+      </c>
+      <c r="AH16" s="0" t="n">
+        <v>0.004943</v>
+      </c>
+      <c r="AI16" s="1" t="n">
         <v>0.330548878263088</v>
       </c>
-      <c r="AH16" s="0" t="n">
+      <c r="AJ16" s="1" t="n">
         <v>0.330548878263088</v>
       </c>
-      <c r="AI16" s="0" t="n">
+      <c r="AK16" s="1" t="n">
         <v>0.330548878263088</v>
       </c>
-      <c r="AJ16" s="0" t="n">
+      <c r="AL16" s="1" t="n">
         <v>0.330548878263088</v>
       </c>
-      <c r="AK16" s="0" t="n">
-        <v>0.330548878263088</v>
-      </c>
-      <c r="AL16" s="0" t="n">
-        <v>0.330548878263088</v>
-      </c>
-      <c r="AO16" s="0" t="s">
+      <c r="AO16" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW16" s="0" t="n">
-        <v>0.330548878263088</v>
+        <v>0.004943</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>0.465269778568085</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <v>0.465269778568085</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <v>0.465269778568085</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <v>0.465269778568085</v>
       </c>
-      <c r="R17" s="0" t="n">
+      <c r="R17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="0" t="n">
+      <c r="S17" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T17" s="0" t="s">
+      <c r="T17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U17" s="1" t="n">
+      <c r="U17" s="2" t="n">
         <v>93.3469615475388</v>
       </c>
-      <c r="V17" s="0" t="n">
+      <c r="V17" s="1" t="n">
         <v>0.336761213881164</v>
       </c>
-      <c r="W17" s="1" t="n">
-        <v>719882797.858835</v>
-      </c>
-      <c r="X17" s="0" t="n">
+      <c r="W17" s="2" t="n">
+        <v>2344</v>
+      </c>
+      <c r="X17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y17" s="0" t="s">
+      <c r="Y17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Z17" s="0" t="s">
+      <c r="Z17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AA17" s="1" t="n">
+      <c r="AA17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
-      <c r="AB17" s="1" t="n">
+      <c r="AB17" s="2" t="n">
         <v>271928468.742695</v>
       </c>
       <c r="AC17" s="0" t="n">
-        <v>0.364087310907066</v>
+        <v>0.005541</v>
       </c>
       <c r="AD17" s="0" t="n">
-        <v>0.364087310907066</v>
+        <v>0.005541</v>
       </c>
       <c r="AE17" s="0" t="n">
-        <v>0.364087310907066</v>
+        <v>0.005541</v>
       </c>
       <c r="AF17" s="0" t="n">
-        <v>0.364087310907066</v>
+        <v>0.005541</v>
       </c>
       <c r="AG17" s="0" t="n">
+        <v>0.005541</v>
+      </c>
+      <c r="AH17" s="0" t="n">
+        <v>0.005541</v>
+      </c>
+      <c r="AI17" s="1" t="n">
         <v>0.336761213881164</v>
       </c>
-      <c r="AH17" s="0" t="n">
+      <c r="AJ17" s="1" t="n">
         <v>0.336761213881164</v>
       </c>
-      <c r="AI17" s="0" t="n">
+      <c r="AK17" s="1" t="n">
         <v>0.336761213881164</v>
       </c>
-      <c r="AJ17" s="0" t="n">
+      <c r="AL17" s="1" t="n">
         <v>0.336761213881164</v>
       </c>
-      <c r="AK17" s="0" t="n">
-        <v>0.336761213881164</v>
-      </c>
-      <c r="AL17" s="0" t="n">
-        <v>0.336761213881164</v>
-      </c>
-      <c r="AO17" s="0" t="s">
+      <c r="AO17" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW17" s="0" t="n">
-        <v>0.336761213881164</v>
+        <v>0.005541</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="I18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="K18" s="0" t="n">
+      <c r="K18" s="1" t="n">
         <v>0.473622301632939</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="1" t="n">
         <v>0.473622301632939</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="1" t="n">
         <v>0.473622301632939</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="1" t="n">
         <v>0.473622301632939</v>
       </c>
-      <c r="R18" s="0" t="n">
+      <c r="R18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S18" s="0" t="n">
+      <c r="S18" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T18" s="0" t="s">
+      <c r="T18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U18" s="1" t="n">
+      <c r="U18" s="2" t="n">
         <v>97.0612371475154</v>
       </c>
-      <c r="V18" s="0" t="n">
+      <c r="V18" s="1" t="n">
         <v>0.343090304134847</v>
       </c>
-      <c r="W18" s="1" t="n">
-        <v>753071835.242812</v>
-      </c>
-      <c r="X18" s="0" t="n">
+      <c r="W18" s="2" t="n">
+        <v>3221</v>
+      </c>
+      <c r="X18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y18" s="0" t="s">
+      <c r="Y18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="Z18" s="0" t="s">
+      <c r="Z18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AA18" s="1" t="n">
+      <c r="AA18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
-      <c r="AB18" s="1" t="n">
+      <c r="AB18" s="2" t="n">
         <v>289473021.617505</v>
       </c>
       <c r="AC18" s="0" t="n">
-        <v>0.372743122636571</v>
+        <v>0.00621</v>
       </c>
       <c r="AD18" s="0" t="n">
-        <v>0.372743122636571</v>
+        <v>0.00621</v>
       </c>
       <c r="AE18" s="0" t="n">
-        <v>0.372743122636571</v>
+        <v>0.00621</v>
       </c>
       <c r="AF18" s="0" t="n">
-        <v>0.372743122636571</v>
+        <v>0.00621</v>
       </c>
       <c r="AG18" s="0" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="AH18" s="0" t="n">
+        <v>0.00621</v>
+      </c>
+      <c r="AI18" s="1" t="n">
         <v>0.343090304134847</v>
       </c>
-      <c r="AH18" s="0" t="n">
+      <c r="AJ18" s="1" t="n">
         <v>0.343090304134847</v>
       </c>
-      <c r="AI18" s="0" t="n">
+      <c r="AK18" s="1" t="n">
         <v>0.343090304134847</v>
       </c>
-      <c r="AJ18" s="0" t="n">
+      <c r="AL18" s="1" t="n">
         <v>0.343090304134847</v>
       </c>
-      <c r="AK18" s="0" t="n">
-        <v>0.343090304134847</v>
-      </c>
-      <c r="AL18" s="0" t="n">
-        <v>0.343090304134847</v>
-      </c>
-      <c r="AO18" s="0" t="s">
+      <c r="AO18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW18" s="0" t="n">
-        <v>0.343090304134847</v>
+        <v>0.00621</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="I19" s="1" t="n">
+      <c r="I19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="K19" s="0" t="n">
+      <c r="K19" s="1" t="n">
         <v>0.482124769191854</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="1" t="n">
         <v>0.482124769191854</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="1" t="n">
         <v>0.482124769191854</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <v>0.482124769191854</v>
       </c>
-      <c r="R19" s="0" t="n">
+      <c r="R19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S19" s="0" t="n">
+      <c r="S19" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T19" s="0" t="s">
+      <c r="T19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U19" s="1" t="n">
+      <c r="U19" s="2" t="n">
         <v>100.923303773615</v>
       </c>
-      <c r="V19" s="0" t="n">
+      <c r="V19" s="1" t="n">
         <v>0.349538343310757</v>
       </c>
-      <c r="W19" s="1" t="n">
-        <v>787790999.761027</v>
-      </c>
-      <c r="X19" s="0" t="n">
+      <c r="W19" s="2" t="n">
+        <v>4424</v>
+      </c>
+      <c r="X19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y19" s="0" t="s">
+      <c r="Y19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Z19" s="0" t="s">
+      <c r="Z19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AA19" s="1" t="n">
+      <c r="AA19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
-      <c r="AB19" s="1" t="n">
+      <c r="AB19" s="2" t="n">
         <v>308149531.499245</v>
       </c>
       <c r="AC19" s="0" t="n">
-        <v>0.381604717634132</v>
+        <v>0.006961</v>
       </c>
       <c r="AD19" s="0" t="n">
-        <v>0.381604717634132</v>
+        <v>0.006961</v>
       </c>
       <c r="AE19" s="0" t="n">
-        <v>0.381604717634132</v>
+        <v>0.006961</v>
       </c>
       <c r="AF19" s="0" t="n">
-        <v>0.381604717634132</v>
+        <v>0.006961</v>
       </c>
       <c r="AG19" s="0" t="n">
+        <v>0.006961</v>
+      </c>
+      <c r="AH19" s="0" t="n">
+        <v>0.006961</v>
+      </c>
+      <c r="AI19" s="1" t="n">
         <v>0.349538343310757</v>
       </c>
-      <c r="AH19" s="0" t="n">
+      <c r="AJ19" s="1" t="n">
         <v>0.349538343310757</v>
       </c>
-      <c r="AI19" s="0" t="n">
+      <c r="AK19" s="1" t="n">
         <v>0.349538343310757</v>
       </c>
-      <c r="AJ19" s="0" t="n">
+      <c r="AL19" s="1" t="n">
         <v>0.349538343310757</v>
       </c>
-      <c r="AK19" s="0" t="n">
-        <v>0.349538343310757</v>
-      </c>
-      <c r="AL19" s="0" t="n">
-        <v>0.349538343310757</v>
-      </c>
-      <c r="AO19" s="0" t="s">
+      <c r="AO19" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW19" s="0" t="n">
-        <v>0.349538343310757</v>
+        <v>0.006961</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="I20" s="1" t="n">
+      <c r="I20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" s="1" t="n">
         <v>0.490779873048386</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <v>0.490779873048386</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <v>0.490779873048386</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="1" t="n">
         <v>0.490779873048386</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="P20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="0" t="n">
+      <c r="Q20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="0" t="n">
+      <c r="R20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S20" s="0" t="n">
+      <c r="S20" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T20" s="0" t="s">
+      <c r="T20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U20" s="1" t="n">
+      <c r="U20" s="2" t="n">
         <v>104.939042030767</v>
       </c>
-      <c r="V20" s="0" t="n">
+      <c r="V20" s="1" t="n">
         <v>0.35610756693494</v>
       </c>
-      <c r="W20" s="1" t="n">
-        <v>824110835.461499</v>
-      </c>
-      <c r="X20" s="0" t="n">
+      <c r="W20" s="2" t="n">
+        <v>6078</v>
+      </c>
+      <c r="X20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y20" s="0" t="s">
+      <c r="Y20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="Z20" s="0" t="s">
+      <c r="Z20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AA20" s="1" t="n">
+      <c r="AA20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
-      <c r="AB20" s="1" t="n">
+      <c r="AB20" s="2" t="n">
         <v>328031031.122044</v>
       </c>
       <c r="AC20" s="0" t="n">
-        <v>0.390676988191166</v>
+        <v>0.007803</v>
       </c>
       <c r="AD20" s="0" t="n">
-        <v>0.390676988191166</v>
+        <v>0.007803</v>
       </c>
       <c r="AE20" s="0" t="n">
-        <v>0.390676988191166</v>
+        <v>0.007803</v>
       </c>
       <c r="AF20" s="0" t="n">
-        <v>0.390676988191166</v>
+        <v>0.007803</v>
       </c>
       <c r="AG20" s="0" t="n">
+        <v>0.007803</v>
+      </c>
+      <c r="AH20" s="0" t="n">
+        <v>0.007803</v>
+      </c>
+      <c r="AI20" s="1" t="n">
         <v>0.35610756693494</v>
       </c>
-      <c r="AH20" s="0" t="n">
+      <c r="AJ20" s="1" t="n">
         <v>0.35610756693494</v>
       </c>
-      <c r="AI20" s="0" t="n">
+      <c r="AK20" s="1" t="n">
         <v>0.35610756693494</v>
       </c>
-      <c r="AJ20" s="0" t="n">
+      <c r="AL20" s="1" t="n">
         <v>0.35610756693494</v>
       </c>
-      <c r="AK20" s="0" t="n">
-        <v>0.35610756693494</v>
-      </c>
-      <c r="AL20" s="0" t="n">
-        <v>0.35610756693494</v>
-      </c>
-      <c r="AM20" s="0" t="s">
+      <c r="AM20" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AN20" s="0" t="n">
+      <c r="AN20" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="AO20" s="0" t="s">
+      <c r="AO20" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW20" s="0" t="n">
-        <v>0.35610756693494</v>
+        <v>0.007803</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="F21" s="1" t="n">
+      <c r="F21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="G21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="I21" s="1" t="n">
+      <c r="I21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="K21" s="0" t="n">
+      <c r="K21" s="1" t="n">
         <v>0.49959035332935</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="1" t="n">
         <v>0.49959035332935</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="1" t="n">
         <v>0.49959035332935</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <v>0.49959035332935</v>
       </c>
-      <c r="R21" s="0" t="n">
+      <c r="R21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S21" s="0" t="n">
+      <c r="S21" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T21" s="0" t="s">
+      <c r="T21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U21" s="1" t="n">
+      <c r="U21" s="2" t="n">
         <v>109.114566513171</v>
       </c>
-      <c r="V21" s="0" t="n">
+      <c r="V21" s="1" t="n">
         <v>0.362800252547915</v>
       </c>
-      <c r="W21" s="1" t="n">
-        <v>862105138.712007</v>
-      </c>
-      <c r="X21" s="0" t="n">
+      <c r="W21" s="2" t="n">
+        <v>8351</v>
+      </c>
+      <c r="X21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y21" s="0" t="s">
+      <c r="Y21" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Z21" s="0" t="s">
+      <c r="Z21" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="AA21" s="1" t="n">
+      <c r="AA21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
-      <c r="AB21" s="1" t="n">
+      <c r="AB21" s="2" t="n">
         <v>349195265.219008</v>
       </c>
       <c r="AC21" s="0" t="n">
-        <v>0.399964942908423</v>
+        <v>0.008746</v>
       </c>
       <c r="AD21" s="0" t="n">
-        <v>0.399964942908423</v>
+        <v>0.008746</v>
       </c>
       <c r="AE21" s="0" t="n">
-        <v>0.399964942908423</v>
+        <v>0.008746</v>
       </c>
       <c r="AF21" s="0" t="n">
-        <v>0.399964942908423</v>
+        <v>0.008746</v>
       </c>
       <c r="AG21" s="0" t="n">
+        <v>0.008746</v>
+      </c>
+      <c r="AH21" s="0" t="n">
+        <v>0.008746</v>
+      </c>
+      <c r="AI21" s="1" t="n">
         <v>0.362800252547915</v>
       </c>
-      <c r="AH21" s="0" t="n">
+      <c r="AJ21" s="1" t="n">
         <v>0.362800252547915</v>
       </c>
-      <c r="AI21" s="0" t="n">
+      <c r="AK21" s="1" t="n">
         <v>0.362800252547915</v>
       </c>
-      <c r="AJ21" s="0" t="n">
+      <c r="AL21" s="1" t="n">
         <v>0.362800252547915</v>
       </c>
-      <c r="AK21" s="0" t="n">
-        <v>0.362800252547915</v>
-      </c>
-      <c r="AL21" s="0" t="n">
-        <v>0.362800252547915</v>
-      </c>
-      <c r="AO21" s="0" t="s">
+      <c r="AO21" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW21" s="0" t="n">
-        <v>0.362800252547915</v>
+        <v>0.008746</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="I22" s="1" t="n">
+      <c r="I22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="K22" s="0" t="n">
+      <c r="K22" s="1" t="n">
         <v>0.508558999352319</v>
       </c>
-      <c r="L22" s="0" t="n">
+      <c r="L22" s="1" t="n">
         <v>0.508558999352319</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="1" t="n">
         <v>0.508558999352319</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="1" t="n">
         <v>0.508558999352319</v>
       </c>
-      <c r="R22" s="0" t="n">
+      <c r="R22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S22" s="0" t="n">
+      <c r="S22" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T22" s="0" t="s">
+      <c r="T22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U22" s="1" t="n">
+      <c r="U22" s="2" t="n">
         <v>113.45623511473</v>
       </c>
-      <c r="V22" s="0" t="n">
+      <c r="V22" s="1" t="n">
         <v>0.3696187204943</v>
       </c>
-      <c r="W22" s="1" t="n">
-        <v>901851108.14305</v>
-      </c>
-      <c r="X22" s="0" t="n">
+      <c r="W22" s="2" t="n">
+        <v>11472</v>
+      </c>
+      <c r="X22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y22" s="0" t="s">
+      <c r="Y22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Z22" s="0" t="s">
+      <c r="Z22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AA22" s="1" t="n">
+      <c r="AA22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
-      <c r="AB22" s="1" t="n">
+      <c r="AB22" s="2" t="n">
         <v>371724994.535673</v>
       </c>
       <c r="AC22" s="0" t="n">
-        <v>0.409473709461128</v>
+        <v>0.009804</v>
       </c>
       <c r="AD22" s="0" t="n">
-        <v>0.409473709461128</v>
+        <v>0.009804</v>
       </c>
       <c r="AE22" s="0" t="n">
-        <v>0.409473709461128</v>
+        <v>0.009804</v>
       </c>
       <c r="AF22" s="0" t="n">
-        <v>0.409473709461128</v>
+        <v>0.009804</v>
       </c>
       <c r="AG22" s="0" t="n">
+        <v>0.009804</v>
+      </c>
+      <c r="AH22" s="0" t="n">
+        <v>0.009804</v>
+      </c>
+      <c r="AI22" s="1" t="n">
         <v>0.3696187204943</v>
       </c>
-      <c r="AH22" s="0" t="n">
+      <c r="AJ22" s="1" t="n">
         <v>0.3696187204943</v>
       </c>
-      <c r="AI22" s="0" t="n">
+      <c r="AK22" s="1" t="n">
         <v>0.3696187204943</v>
       </c>
-      <c r="AJ22" s="0" t="n">
+      <c r="AL22" s="1" t="n">
         <v>0.3696187204943</v>
       </c>
-      <c r="AK22" s="0" t="n">
-        <v>0.3696187204943</v>
-      </c>
-      <c r="AL22" s="0" t="n">
-        <v>0.3696187204943</v>
-      </c>
-      <c r="AO22" s="0" t="s">
+      <c r="AO22" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW22" s="0" t="n">
-        <v>0.3696187204943</v>
+        <v>0.009804</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="F23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="G23" s="1" t="n">
+      <c r="G23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="I23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="K23" s="0" t="n">
+      <c r="K23" s="1" t="n">
         <v>0.517688650508692</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="1" t="n">
         <v>0.517688650508692</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="1" t="n">
         <v>0.517688650508692</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="1" t="n">
         <v>0.517688650508692</v>
       </c>
-      <c r="R23" s="0" t="n">
+      <c r="R23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S23" s="0" t="n">
+      <c r="S23" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T23" s="0" t="s">
+      <c r="T23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U23" s="1" t="n">
+      <c r="U23" s="2" t="n">
         <v>117.970658709946</v>
       </c>
-      <c r="V23" s="0" t="n">
+      <c r="V23" s="1" t="n">
         <v>0.37656533472727</v>
       </c>
-      <c r="W23" s="1" t="n">
-        <v>943429501.503702</v>
-      </c>
-      <c r="X23" s="0" t="n">
+      <c r="W23" s="2" t="n">
+        <v>15761</v>
+      </c>
+      <c r="X23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y23" s="0" t="s">
+      <c r="Y23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Z23" s="0" t="s">
+      <c r="Z23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AA23" s="1" t="n">
+      <c r="AA23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
-      <c r="AB23" s="1" t="n">
+      <c r="AB23" s="2" t="n">
         <v>395708319.45812</v>
       </c>
       <c r="AC23" s="0" t="n">
-        <v>0.419208537429857</v>
+        <v>0.010989</v>
       </c>
       <c r="AD23" s="0" t="n">
-        <v>0.419208537429857</v>
+        <v>0.010989</v>
       </c>
       <c r="AE23" s="0" t="n">
-        <v>0.419208537429857</v>
+        <v>0.010989</v>
       </c>
       <c r="AF23" s="0" t="n">
-        <v>0.419208537429857</v>
+        <v>0.010989</v>
       </c>
       <c r="AG23" s="0" t="n">
+        <v>0.010989</v>
+      </c>
+      <c r="AH23" s="0" t="n">
+        <v>0.010989</v>
+      </c>
+      <c r="AI23" s="1" t="n">
         <v>0.37656533472727</v>
       </c>
-      <c r="AH23" s="0" t="n">
+      <c r="AJ23" s="1" t="n">
         <v>0.37656533472727</v>
       </c>
-      <c r="AI23" s="0" t="n">
+      <c r="AK23" s="1" t="n">
         <v>0.37656533472727</v>
       </c>
-      <c r="AJ23" s="0" t="n">
+      <c r="AL23" s="1" t="n">
         <v>0.37656533472727</v>
       </c>
-      <c r="AK23" s="0" t="n">
-        <v>0.37656533472727</v>
-      </c>
-      <c r="AL23" s="0" t="n">
-        <v>0.37656533472727</v>
-      </c>
-      <c r="AO23" s="0" t="s">
+      <c r="AO23" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW23" s="0" t="n">
-        <v>0.37656533472727</v>
+        <v>0.010989</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="F24" s="1" t="n">
+      <c r="F24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="G24" s="1" t="n">
+      <c r="G24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="I24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="K24" s="1" t="n">
         <v>0.526982197162624</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24" s="1" t="n">
         <v>0.526982197162624</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="1" t="n">
         <v>0.526982197162624</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="1" t="n">
         <v>0.526982197162624</v>
       </c>
-      <c r="R24" s="0" t="n">
+      <c r="R24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S24" s="0" t="n">
+      <c r="S24" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T24" s="0" t="s">
+      <c r="T24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="1" t="n">
+      <c r="U24" s="2" t="n">
         <v>122.664711220014</v>
       </c>
-      <c r="V24" s="0" t="n">
+      <c r="V24" s="1" t="n">
         <v>0.383642503628135</v>
       </c>
-      <c r="W24" s="1" t="n">
-        <v>986924799.749033</v>
-      </c>
-      <c r="X24" s="0" t="n">
+      <c r="W24" s="2" t="n">
+        <v>21653</v>
+      </c>
+      <c r="X24" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="0" t="s">
+      <c r="Y24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Z24" s="0" t="s">
+      <c r="Z24" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="AA24" s="1" t="n">
+      <c r="AA24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
-      <c r="AB24" s="1" t="n">
+      <c r="AB24" s="2" t="n">
         <v>421239024.521238</v>
       </c>
       <c r="AC24" s="0" t="n">
-        <v>0.429174801198714</v>
+        <v>0.012318</v>
       </c>
       <c r="AD24" s="0" t="n">
-        <v>0.429174801198714</v>
+        <v>0.012318</v>
       </c>
       <c r="AE24" s="0" t="n">
-        <v>0.429174801198714</v>
+        <v>0.012318</v>
       </c>
       <c r="AF24" s="0" t="n">
-        <v>0.429174801198714</v>
+        <v>0.012318</v>
       </c>
       <c r="AG24" s="0" t="n">
+        <v>0.012318</v>
+      </c>
+      <c r="AH24" s="0" t="n">
+        <v>0.012318</v>
+      </c>
+      <c r="AI24" s="1" t="n">
         <v>0.383642503628135</v>
       </c>
-      <c r="AH24" s="0" t="n">
+      <c r="AJ24" s="1" t="n">
         <v>0.383642503628135</v>
       </c>
-      <c r="AI24" s="0" t="n">
+      <c r="AK24" s="1" t="n">
         <v>0.383642503628135</v>
       </c>
-      <c r="AJ24" s="0" t="n">
+      <c r="AL24" s="1" t="n">
         <v>0.383642503628135</v>
       </c>
-      <c r="AK24" s="0" t="n">
-        <v>0.383642503628135</v>
-      </c>
-      <c r="AL24" s="0" t="n">
-        <v>0.383642503628135</v>
-      </c>
-      <c r="AO24" s="0" t="s">
+      <c r="AO24" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW24" s="0" t="n">
-        <v>0.383642503628135</v>
+        <v>0.012318</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="F25" s="1" t="n">
+      <c r="F25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="G25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="H25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="I25" s="1" t="n">
+      <c r="I25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="K25" s="1" t="n">
         <v>0.536442581566087</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="1" t="n">
         <v>0.536442581566087</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="1" t="n">
         <v>0.536442581566087</v>
       </c>
-      <c r="N25" s="0" t="n">
+      <c r="N25" s="1" t="n">
         <v>0.536442581566087</v>
       </c>
-      <c r="R25" s="0" t="n">
+      <c r="R25" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S25" s="0" t="n">
+      <c r="S25" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T25" s="0" t="s">
+      <c r="T25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U25" s="1" t="n">
+      <c r="U25" s="2" t="n">
         <v>127.545540079459</v>
       </c>
-      <c r="V25" s="0" t="n">
+      <c r="V25" s="1" t="n">
         <v>0.390852680841322</v>
       </c>
-      <c r="W25" s="1" t="n">
-        <v>1032425378.69253</v>
-      </c>
-      <c r="X25" s="0" t="n">
+      <c r="W25" s="2" t="n">
+        <v>29747</v>
+      </c>
+      <c r="X25" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y25" s="0" t="s">
+      <c r="Y25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Z25" s="0" t="s">
+      <c r="Z25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AA25" s="1" t="n">
+      <c r="AA25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
-      <c r="AB25" s="1" t="n">
+      <c r="AB25" s="2" t="n">
         <v>448416945.144324</v>
       </c>
       <c r="AC25" s="0" t="n">
-        <v>0.439378002922412</v>
+        <v>0.013807</v>
       </c>
       <c r="AD25" s="0" t="n">
-        <v>0.439378002922412</v>
+        <v>0.013807</v>
       </c>
       <c r="AE25" s="0" t="n">
-        <v>0.439378002922412</v>
+        <v>0.013807</v>
       </c>
       <c r="AF25" s="0" t="n">
-        <v>0.439378002922412</v>
+        <v>0.013807</v>
       </c>
       <c r="AG25" s="0" t="n">
+        <v>0.013807</v>
+      </c>
+      <c r="AH25" s="0" t="n">
+        <v>0.013807</v>
+      </c>
+      <c r="AI25" s="1" t="n">
         <v>0.390852680841322</v>
       </c>
-      <c r="AH25" s="0" t="n">
+      <c r="AJ25" s="1" t="n">
         <v>0.390852680841322</v>
       </c>
-      <c r="AI25" s="0" t="n">
+      <c r="AK25" s="1" t="n">
         <v>0.390852680841322</v>
       </c>
-      <c r="AJ25" s="0" t="n">
+      <c r="AL25" s="1" t="n">
         <v>0.390852680841322</v>
       </c>
-      <c r="AK25" s="0" t="n">
-        <v>0.390852680841322</v>
-      </c>
-      <c r="AL25" s="0" t="n">
-        <v>0.390852680841322</v>
-      </c>
-      <c r="AO25" s="0" t="s">
+      <c r="AO25" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW25" s="0" t="n">
-        <v>0.390852680841322</v>
+        <v>0.013807</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="F26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="G26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="H26" s="1" t="n">
+      <c r="H26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="I26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="K26" s="0" t="n">
+      <c r="K26" s="1" t="n">
         <v>0.546072798790361</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="1" t="n">
         <v>0.546072798790361</v>
       </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.546072798790361</v>
       </c>
-      <c r="N26" s="0" t="n">
+      <c r="N26" s="1" t="n">
         <v>0.546072798790361</v>
       </c>
-      <c r="R26" s="0" t="n">
+      <c r="R26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S26" s="0" t="n">
+      <c r="S26" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T26" s="0" t="s">
+      <c r="T26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U26" s="1" t="n">
+      <c r="U26" s="2" t="n">
         <v>132.62057711922</v>
       </c>
-      <c r="V26" s="0" t="n">
+      <c r="V26" s="1" t="n">
         <v>0.398198366125053</v>
       </c>
-      <c r="W26" s="1" t="n">
-        <v>1080023688.57229</v>
-      </c>
-      <c r="X26" s="0" t="n">
+      <c r="W26" s="2" t="n">
+        <v>40867</v>
+      </c>
+      <c r="X26" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y26" s="0" t="s">
+      <c r="Y26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Z26" s="0" t="s">
+      <c r="Z26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AA26" s="1" t="n">
+      <c r="AA26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
-      <c r="AB26" s="1" t="n">
+      <c r="AB26" s="2" t="n">
         <v>477348358.028091</v>
       </c>
       <c r="AC26" s="0" t="n">
-        <v>0.44982377556389</v>
+        <v>0.015477</v>
       </c>
       <c r="AD26" s="0" t="n">
-        <v>0.44982377556389</v>
+        <v>0.015477</v>
       </c>
       <c r="AE26" s="0" t="n">
-        <v>0.44982377556389</v>
+        <v>0.015477</v>
       </c>
       <c r="AF26" s="0" t="n">
-        <v>0.44982377556389</v>
+        <v>0.015477</v>
       </c>
       <c r="AG26" s="0" t="n">
+        <v>0.015477</v>
+      </c>
+      <c r="AH26" s="0" t="n">
+        <v>0.015477</v>
+      </c>
+      <c r="AI26" s="1" t="n">
         <v>0.398198366125053</v>
       </c>
-      <c r="AH26" s="0" t="n">
+      <c r="AJ26" s="1" t="n">
         <v>0.398198366125053</v>
       </c>
-      <c r="AI26" s="0" t="n">
+      <c r="AK26" s="1" t="n">
         <v>0.398198366125053</v>
       </c>
-      <c r="AJ26" s="0" t="n">
+      <c r="AL26" s="1" t="n">
         <v>0.398198366125053</v>
       </c>
-      <c r="AK26" s="0" t="n">
-        <v>0.398198366125053</v>
-      </c>
-      <c r="AL26" s="0" t="n">
-        <v>0.398198366125053</v>
-      </c>
-      <c r="AO26" s="0" t="s">
+      <c r="AO26" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW26" s="0" t="n">
-        <v>0.398198366125053</v>
+        <v>0.015477</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="F27" s="1" t="n">
+      <c r="F27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="G27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="H27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="K27" s="1" t="n">
         <v>0.555875897674246</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="1" t="n">
         <v>0.555875897674246</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27" s="1" t="n">
         <v>0.555875897674246</v>
       </c>
-      <c r="N27" s="0" t="n">
+      <c r="N27" s="1" t="n">
         <v>0.555875897674246</v>
       </c>
-      <c r="R27" s="0" t="n">
+      <c r="R27" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S27" s="0" t="n">
+      <c r="S27" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T27" s="0" t="s">
+      <c r="T27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U27" s="1" t="n">
+      <c r="U27" s="2" t="n">
         <v>137.897549882794</v>
       </c>
-      <c r="V27" s="0" t="n">
+      <c r="V27" s="1" t="n">
         <v>0.405682106218008</v>
       </c>
-      <c r="W27" s="1" t="n">
-        <v>1129816441.89578</v>
-      </c>
-      <c r="X27" s="0" t="n">
+      <c r="W27" s="2" t="n">
+        <v>56144</v>
+      </c>
+      <c r="X27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y27" s="0" t="s">
+      <c r="Y27" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Z27" s="0" t="s">
+      <c r="Z27" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AA27" s="1" t="n">
+      <c r="AA27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
-      <c r="AB27" s="1" t="n">
+      <c r="AB27" s="2" t="n">
         <v>508146396.739705</v>
       </c>
       <c r="AC27" s="0" t="n">
-        <v>0.460517886004146</v>
+        <v>0.017348</v>
       </c>
       <c r="AD27" s="0" t="n">
-        <v>0.460517886004146</v>
+        <v>0.017348</v>
       </c>
       <c r="AE27" s="0" t="n">
-        <v>0.460517886004146</v>
+        <v>0.017348</v>
       </c>
       <c r="AF27" s="0" t="n">
-        <v>0.460517886004146</v>
+        <v>0.017348</v>
       </c>
       <c r="AG27" s="0" t="n">
+        <v>0.017348</v>
+      </c>
+      <c r="AH27" s="0" t="n">
+        <v>0.017348</v>
+      </c>
+      <c r="AI27" s="1" t="n">
         <v>0.405682106218008</v>
       </c>
-      <c r="AH27" s="0" t="n">
+      <c r="AJ27" s="1" t="n">
         <v>0.405682106218008</v>
       </c>
-      <c r="AI27" s="0" t="n">
+      <c r="AK27" s="1" t="n">
         <v>0.405682106218008</v>
       </c>
-      <c r="AJ27" s="0" t="n">
+      <c r="AL27" s="1" t="n">
         <v>0.405682106218008</v>
       </c>
-      <c r="AK27" s="0" t="n">
-        <v>0.405682106218008</v>
-      </c>
-      <c r="AL27" s="0" t="n">
-        <v>0.405682106218008</v>
-      </c>
-      <c r="AO27" s="0" t="s">
+      <c r="AO27" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW27" s="0" t="n">
-        <v>0.405682106218008</v>
+        <v>0.017348</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="F28" s="1" t="n">
+      <c r="F28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="G28" s="1" t="n">
+      <c r="G28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="I28" s="1" t="n">
+      <c r="I28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="K28" s="0" t="n">
+      <c r="K28" s="1" t="n">
         <v>0.565854981789294</v>
       </c>
-      <c r="L28" s="0" t="n">
+      <c r="L28" s="1" t="n">
         <v>0.565854981789294</v>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="M28" s="1" t="n">
         <v>0.565854981789294</v>
       </c>
-      <c r="N28" s="0" t="n">
+      <c r="N28" s="1" t="n">
         <v>0.565854981789294</v>
       </c>
-      <c r="R28" s="0" t="n">
+      <c r="R28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S28" s="0" t="n">
+      <c r="S28" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T28" s="0" t="s">
+      <c r="T28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U28" s="1" t="n">
+      <c r="U28" s="2" t="n">
         <v>143.384493392631</v>
       </c>
-      <c r="V28" s="0" t="n">
+      <c r="V28" s="1" t="n">
         <v>0.413306495722269</v>
       </c>
-      <c r="W28" s="1" t="n">
-        <v>1181904809.94491</v>
-      </c>
-      <c r="X28" s="0" t="n">
+      <c r="W28" s="2" t="n">
+        <v>77132</v>
+      </c>
+      <c r="X28" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y28" s="0" t="s">
+      <c r="Y28" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="Z28" s="0" t="s">
+      <c r="Z28" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AA28" s="1" t="n">
+      <c r="AA28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
-      <c r="AB28" s="1" t="n">
+      <c r="AB28" s="2" t="n">
         <v>540931494.110954</v>
       </c>
       <c r="AC28" s="0" t="n">
-        <v>0.471466238226008</v>
+        <v>0.019446</v>
       </c>
       <c r="AD28" s="0" t="n">
-        <v>0.471466238226008</v>
+        <v>0.019446</v>
       </c>
       <c r="AE28" s="0" t="n">
-        <v>0.471466238226008</v>
+        <v>0.019446</v>
       </c>
       <c r="AF28" s="0" t="n">
-        <v>0.471466238226008</v>
+        <v>0.019446</v>
       </c>
       <c r="AG28" s="0" t="n">
+        <v>0.019446</v>
+      </c>
+      <c r="AH28" s="0" t="n">
+        <v>0.019446</v>
+      </c>
+      <c r="AI28" s="1" t="n">
         <v>0.413306495722269</v>
       </c>
-      <c r="AH28" s="0" t="n">
+      <c r="AJ28" s="1" t="n">
         <v>0.413306495722269</v>
       </c>
-      <c r="AI28" s="0" t="n">
+      <c r="AK28" s="1" t="n">
         <v>0.413306495722269</v>
       </c>
-      <c r="AJ28" s="0" t="n">
+      <c r="AL28" s="1" t="n">
         <v>0.413306495722269</v>
       </c>
-      <c r="AK28" s="0" t="n">
-        <v>0.413306495722269</v>
-      </c>
-      <c r="AL28" s="0" t="n">
-        <v>0.413306495722269</v>
-      </c>
-      <c r="AO28" s="0" t="s">
+      <c r="AO28" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW28" s="0" t="n">
-        <v>0.413306495722269</v>
+        <v>0.019446</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="F29" s="1" t="n">
+      <c r="F29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="G29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="H29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="I29" s="1" t="n">
+      <c r="I29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="K29" s="0" t="n">
+      <c r="K29" s="1" t="n">
         <v>0.576013210422375</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L29" s="1" t="n">
         <v>0.576013210422375</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M29" s="1" t="n">
         <v>0.576013210422375</v>
       </c>
-      <c r="N29" s="0" t="n">
+      <c r="N29" s="1" t="n">
         <v>0.576013210422375</v>
       </c>
-      <c r="R29" s="0" t="n">
+      <c r="R29" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S29" s="0" t="n">
+      <c r="S29" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T29" s="0" t="s">
+      <c r="T29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U29" s="1" t="n">
+      <c r="U29" s="2" t="n">
         <v>149.089762384723</v>
       </c>
-      <c r="V29" s="0" t="n">
+      <c r="V29" s="1" t="n">
         <v>0.421074178002873</v>
       </c>
-      <c r="W29" s="1" t="n">
-        <v>1236394628.34068</v>
-      </c>
-      <c r="X29" s="0" t="n">
+      <c r="W29" s="2" t="n">
+        <v>105966</v>
+      </c>
+      <c r="X29" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y29" s="0" t="s">
+      <c r="Y29" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="Z29" s="0" t="s">
+      <c r="Z29" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="AA29" s="1" t="n">
+      <c r="AA29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
-      <c r="AB29" s="1" t="n">
+      <c r="AB29" s="2" t="n">
         <v>575831853.179499</v>
       </c>
       <c r="AC29" s="0" t="n">
-        <v>0.482674876573593</v>
+        <v>0.021797</v>
       </c>
       <c r="AD29" s="0" t="n">
-        <v>0.482674876573593</v>
+        <v>0.021797</v>
       </c>
       <c r="AE29" s="0" t="n">
-        <v>0.482674876573593</v>
+        <v>0.021797</v>
       </c>
       <c r="AF29" s="0" t="n">
-        <v>0.482674876573593</v>
+        <v>0.021797</v>
       </c>
       <c r="AG29" s="0" t="n">
+        <v>0.021797</v>
+      </c>
+      <c r="AH29" s="0" t="n">
+        <v>0.021797</v>
+      </c>
+      <c r="AI29" s="1" t="n">
         <v>0.421074178002873</v>
       </c>
-      <c r="AH29" s="0" t="n">
+      <c r="AJ29" s="1" t="n">
         <v>0.421074178002873</v>
       </c>
-      <c r="AI29" s="0" t="n">
+      <c r="AK29" s="1" t="n">
         <v>0.421074178002873</v>
       </c>
-      <c r="AJ29" s="0" t="n">
+      <c r="AL29" s="1" t="n">
         <v>0.421074178002873</v>
       </c>
-      <c r="AK29" s="0" t="n">
-        <v>0.421074178002873</v>
-      </c>
-      <c r="AL29" s="0" t="n">
-        <v>0.421074178002873</v>
-      </c>
-      <c r="AO29" s="0" t="s">
+      <c r="AO29" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW29" s="0" t="n">
-        <v>0.421074178002873</v>
+        <v>0.021797</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>175</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="F30" s="1" t="n">
+      <c r="F30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="G30" s="1" t="n">
+      <c r="G30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="I30" s="1" t="n">
+      <c r="I30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="K30" s="0" t="n">
+      <c r="K30" s="1" t="n">
         <v>0.586353799575878</v>
       </c>
-      <c r="L30" s="0" t="n">
+      <c r="L30" s="1" t="n">
         <v>0.586353799575878</v>
       </c>
-      <c r="M30" s="0" t="n">
+      <c r="M30" s="1" t="n">
         <v>0.586353799575878</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N30" s="1" t="n">
         <v>0.586353799575878</v>
       </c>
-      <c r="R30" s="0" t="n">
+      <c r="R30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S30" s="0" t="n">
+      <c r="S30" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T30" s="0" t="s">
+      <c r="T30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U30" s="1" t="n">
+      <c r="U30" s="2" t="n">
         <v>155.022044030011</v>
       </c>
-      <c r="V30" s="0" t="n">
+      <c r="V30" s="1" t="n">
         <v>0.428987846104259</v>
       </c>
-      <c r="W30" s="1" t="n">
-        <v>1293396612.08498</v>
-      </c>
-      <c r="X30" s="0" t="n">
+      <c r="W30" s="2" t="n">
+        <v>145579</v>
+      </c>
+      <c r="X30" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" s="0" t="s">
+      <c r="Y30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Z30" s="0" t="s">
+      <c r="Z30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="AA30" s="1" t="n">
+      <c r="AA30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
-      <c r="AB30" s="1" t="n">
+      <c r="AB30" s="2" t="n">
         <v>612983948.514787</v>
       </c>
       <c r="AC30" s="0" t="n">
-        <v>0.494149989089254</v>
+        <v>0.024432</v>
       </c>
       <c r="AD30" s="0" t="n">
-        <v>0.494149989089254</v>
+        <v>0.024432</v>
       </c>
       <c r="AE30" s="0" t="n">
-        <v>0.494149989089254</v>
+        <v>0.024432</v>
       </c>
       <c r="AF30" s="0" t="n">
-        <v>0.494149989089254</v>
+        <v>0.024432</v>
       </c>
       <c r="AG30" s="0" t="n">
+        <v>0.024432</v>
+      </c>
+      <c r="AH30" s="0" t="n">
+        <v>0.024432</v>
+      </c>
+      <c r="AI30" s="1" t="n">
         <v>0.428987846104259</v>
       </c>
-      <c r="AH30" s="0" t="n">
+      <c r="AJ30" s="1" t="n">
         <v>0.428987846104259</v>
       </c>
-      <c r="AI30" s="0" t="n">
+      <c r="AK30" s="1" t="n">
         <v>0.428987846104259</v>
       </c>
-      <c r="AJ30" s="0" t="n">
+      <c r="AL30" s="1" t="n">
         <v>0.428987846104259</v>
       </c>
-      <c r="AK30" s="0" t="n">
-        <v>0.428987846104259</v>
-      </c>
-      <c r="AL30" s="0" t="n">
-        <v>0.428987846104259</v>
-      </c>
-      <c r="AO30" s="0" t="s">
+      <c r="AO30" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW30" s="0" t="n">
-        <v>0.428987846104259</v>
+        <v>0.024432</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>176</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="F31" s="1" t="n">
+      <c r="F31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="G31" s="1" t="n">
+      <c r="G31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="I31" s="1" t="n">
+      <c r="I31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="K31" s="0" t="n">
+      <c r="K31" s="1" t="n">
         <v>0.596880022985864</v>
       </c>
-      <c r="L31" s="0" t="n">
+      <c r="L31" s="1" t="n">
         <v>0.596880022985864</v>
       </c>
-      <c r="M31" s="0" t="n">
+      <c r="M31" s="1" t="n">
         <v>0.596880022985864</v>
       </c>
-      <c r="N31" s="0" t="n">
+      <c r="N31" s="1" t="n">
         <v>0.596880022985864</v>
       </c>
-      <c r="R31" s="0" t="n">
+      <c r="R31" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S31" s="0" t="n">
+      <c r="S31" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T31" s="0" t="s">
+      <c r="T31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U31" s="1" t="n">
+      <c r="U31" s="2" t="n">
         <v>161.190371161966</v>
       </c>
-      <c r="V31" s="0" t="n">
+      <c r="V31" s="1" t="n">
         <v>0.437050243683943</v>
       </c>
-      <c r="W31" s="1" t="n">
-        <v>1353026580.51661</v>
-      </c>
-      <c r="X31" s="0" t="n">
+      <c r="W31" s="2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="X31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y31" s="0" t="s">
+      <c r="Y31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Z31" s="0" t="s">
+      <c r="Z31" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AA31" s="1" t="n">
+      <c r="AA31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
-      <c r="AB31" s="1" t="n">
+      <c r="AB31" s="2" t="n">
         <v>652533059.889012</v>
       </c>
       <c r="AC31" s="0" t="n">
-        <v>0.505897910929862</v>
+        <v>0.027386</v>
       </c>
       <c r="AD31" s="0" t="n">
-        <v>0.505897910929862</v>
+        <v>0.027386</v>
       </c>
       <c r="AE31" s="0" t="n">
-        <v>0.505897910929862</v>
+        <v>0.027386</v>
       </c>
       <c r="AF31" s="0" t="n">
-        <v>0.505897910929862</v>
+        <v>0.027386</v>
       </c>
       <c r="AG31" s="0" t="n">
+        <v>0.027386</v>
+      </c>
+      <c r="AH31" s="0" t="n">
+        <v>0.027386</v>
+      </c>
+      <c r="AI31" s="1" t="n">
         <v>0.437050243683943</v>
       </c>
-      <c r="AH31" s="0" t="n">
+      <c r="AJ31" s="1" t="n">
         <v>0.437050243683943</v>
       </c>
-      <c r="AI31" s="0" t="n">
+      <c r="AK31" s="1" t="n">
         <v>0.437050243683943</v>
       </c>
-      <c r="AJ31" s="0" t="n">
+      <c r="AL31" s="1" t="n">
         <v>0.437050243683943</v>
       </c>
-      <c r="AK31" s="0" t="n">
-        <v>0.437050243683943</v>
-      </c>
-      <c r="AL31" s="0" t="n">
-        <v>0.437050243683943</v>
-      </c>
-      <c r="AO31" s="0" t="s">
+      <c r="AO31" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW31" s="0" t="n">
-        <v>0.437050243683943</v>
+        <v>0.027386</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="1" t="n">
         <v>177</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="F32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="G32" s="1" t="n">
+      <c r="G32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="H32" s="1" t="n">
+      <c r="H32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="I32" s="1" t="n">
+      <c r="I32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="K32" s="0" t="n">
+      <c r="K32" s="1" t="n">
         <v>0.607595213158506</v>
       </c>
-      <c r="L32" s="0" t="n">
+      <c r="L32" s="1" t="n">
         <v>0.607595213158506</v>
       </c>
-      <c r="M32" s="0" t="n">
+      <c r="M32" s="1" t="n">
         <v>0.607595213158506</v>
       </c>
-      <c r="N32" s="0" t="n">
+      <c r="N32" s="1" t="n">
         <v>0.607595213158506</v>
       </c>
-      <c r="R32" s="0" t="n">
+      <c r="R32" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S32" s="0" t="n">
+      <c r="S32" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T32" s="0" t="s">
+      <c r="T32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U32" s="1" t="n">
+      <c r="U32" s="2" t="n">
         <v>167.6041360305</v>
       </c>
-      <c r="V32" s="0" t="n">
+      <c r="V32" s="1" t="n">
         <v>0.445264165963739</v>
       </c>
-      <c r="W32" s="1" t="n">
-        <v>1415405692.63853</v>
-      </c>
-      <c r="X32" s="0" t="n">
+      <c r="W32" s="2" t="n">
+        <v>274765</v>
+      </c>
+      <c r="X32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" s="0" t="s">
+      <c r="Y32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Z32" s="0" t="s">
+      <c r="Z32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA32" s="1" t="n">
+      <c r="AA32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
-      <c r="AB32" s="1" t="n">
+      <c r="AB32" s="2" t="n">
         <v>694633840.379992</v>
       </c>
       <c r="AC32" s="0" t="n">
-        <v>0.517925127864308</v>
+        <v>0.030697</v>
       </c>
       <c r="AD32" s="0" t="n">
-        <v>0.517925127864308</v>
+        <v>0.030697</v>
       </c>
       <c r="AE32" s="0" t="n">
-        <v>0.517925127864308</v>
+        <v>0.030697</v>
       </c>
       <c r="AF32" s="0" t="n">
-        <v>0.517925127864308</v>
+        <v>0.030697</v>
       </c>
       <c r="AG32" s="0" t="n">
+        <v>0.030697</v>
+      </c>
+      <c r="AH32" s="0" t="n">
+        <v>0.030697</v>
+      </c>
+      <c r="AI32" s="1" t="n">
         <v>0.445264165963739</v>
       </c>
-      <c r="AH32" s="0" t="n">
+      <c r="AJ32" s="1" t="n">
         <v>0.445264165963739</v>
       </c>
-      <c r="AI32" s="0" t="n">
+      <c r="AK32" s="1" t="n">
         <v>0.445264165963739</v>
       </c>
-      <c r="AJ32" s="0" t="n">
+      <c r="AL32" s="1" t="n">
         <v>0.445264165963739</v>
       </c>
-      <c r="AK32" s="0" t="n">
-        <v>0.445264165963739</v>
-      </c>
-      <c r="AL32" s="0" t="n">
-        <v>0.445264165963739</v>
-      </c>
-      <c r="AO32" s="0" t="s">
+      <c r="AO32" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW32" s="0" t="n">
-        <v>0.445264165963739</v>
+        <v>0.030697</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="1" t="n">
         <v>178</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="F33" s="1" t="n">
+      <c r="F33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="G33" s="1" t="n">
+      <c r="G33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="H33" s="1" t="n">
+      <c r="H33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="I33" s="1" t="n">
+      <c r="I33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="K33" s="0" t="n">
+      <c r="K33" s="1" t="n">
         <v>0.618502762425128</v>
       </c>
-      <c r="L33" s="0" t="n">
+      <c r="L33" s="1" t="n">
         <v>0.618502762425128</v>
       </c>
-      <c r="M33" s="0" t="n">
+      <c r="M33" s="1" t="n">
         <v>0.618502762425128</v>
       </c>
-      <c r="N33" s="0" t="n">
+      <c r="N33" s="1" t="n">
         <v>0.618502762425128</v>
       </c>
-      <c r="R33" s="0" t="n">
+      <c r="R33" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S33" s="0" t="n">
+      <c r="S33" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T33" s="0" t="s">
+      <c r="T33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U33" s="1" t="n">
+      <c r="U33" s="2" t="n">
         <v>174.273104603154</v>
       </c>
-      <c r="V33" s="0" t="n">
+      <c r="V33" s="1" t="n">
         <v>0.453632460698861</v>
       </c>
-      <c r="W33" s="1" t="n">
-        <v>1480660693.29447</v>
-      </c>
-      <c r="X33" s="0" t="n">
+      <c r="W33" s="2" t="n">
+        <v>377478</v>
+      </c>
+      <c r="X33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" s="0" t="s">
+      <c r="Y33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Z33" s="0" t="s">
+      <c r="Z33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AA33" s="1" t="n">
+      <c r="AA33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
-      <c r="AB33" s="1" t="n">
+      <c r="AB33" s="2" t="n">
         <v>739450921.127468</v>
       </c>
       <c r="AC33" s="0" t="n">
-        <v>0.530238279854154</v>
+        <v>0.034409</v>
       </c>
       <c r="AD33" s="0" t="n">
-        <v>0.530238279854154</v>
+        <v>0.034409</v>
       </c>
       <c r="AE33" s="0" t="n">
-        <v>0.530238279854154</v>
+        <v>0.034409</v>
       </c>
       <c r="AF33" s="0" t="n">
-        <v>0.530238279854154</v>
+        <v>0.034409</v>
       </c>
       <c r="AG33" s="0" t="n">
+        <v>0.034409</v>
+      </c>
+      <c r="AH33" s="0" t="n">
+        <v>0.034409</v>
+      </c>
+      <c r="AI33" s="1" t="n">
         <v>0.453632460698861</v>
       </c>
-      <c r="AH33" s="0" t="n">
+      <c r="AJ33" s="1" t="n">
         <v>0.453632460698861</v>
       </c>
-      <c r="AI33" s="0" t="n">
+      <c r="AK33" s="1" t="n">
         <v>0.453632460698861</v>
       </c>
-      <c r="AJ33" s="0" t="n">
+      <c r="AL33" s="1" t="n">
         <v>0.453632460698861</v>
       </c>
-      <c r="AK33" s="0" t="n">
-        <v>0.453632460698861</v>
-      </c>
-      <c r="AL33" s="0" t="n">
-        <v>0.453632460698861</v>
-      </c>
-      <c r="AO33" s="0" t="s">
+      <c r="AO33" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW33" s="0" t="n">
-        <v>0.453632460698861</v>
+        <v>0.034409</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="1" t="n">
         <v>179</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="F34" s="1" t="n">
+      <c r="F34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="G34" s="1" t="n">
+      <c r="G34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="I34" s="1" t="n">
+      <c r="I34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="K34" s="0" t="n">
+      <c r="K34" s="1" t="n">
         <v>0.629606124016184</v>
       </c>
-      <c r="L34" s="0" t="n">
+      <c r="L34" s="1" t="n">
         <v>0.629606124016184</v>
       </c>
-      <c r="M34" s="0" t="n">
+      <c r="M34" s="1" t="n">
         <v>0.629606124016184</v>
       </c>
-      <c r="N34" s="0" t="n">
+      <c r="N34" s="1" t="n">
         <v>0.629606124016184</v>
       </c>
-      <c r="R34" s="0" t="n">
+      <c r="R34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S34" s="0" t="n">
+      <c r="S34" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T34" s="0" t="s">
+      <c r="T34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U34" s="1" t="n">
+      <c r="U34" s="2" t="n">
         <v>181.207431435313</v>
       </c>
-      <c r="V34" s="0" t="n">
+      <c r="V34" s="1" t="n">
         <v>0.462158029165236</v>
       </c>
-      <c r="W34" s="1" t="n">
-        <v>1548924170.69509</v>
-      </c>
-      <c r="X34" s="0" t="n">
+      <c r="W34" s="2" t="n">
+        <v>518589</v>
+      </c>
+      <c r="X34" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y34" s="0" t="s">
+      <c r="Y34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="Z34" s="0" t="s">
+      <c r="Z34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AA34" s="1" t="n">
+      <c r="AA34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
-      <c r="AB34" s="1" t="n">
+      <c r="AB34" s="2" t="n">
         <v>787159555.107691</v>
       </c>
       <c r="AC34" s="0" t="n">
-        <v>0.542844164719407</v>
+        <v>0.038569</v>
       </c>
       <c r="AD34" s="0" t="n">
-        <v>0.542844164719407</v>
+        <v>0.038569</v>
       </c>
       <c r="AE34" s="0" t="n">
-        <v>0.542844164719407</v>
+        <v>0.038569</v>
       </c>
       <c r="AF34" s="0" t="n">
-        <v>0.542844164719407</v>
+        <v>0.038569</v>
       </c>
       <c r="AG34" s="0" t="n">
+        <v>0.038569</v>
+      </c>
+      <c r="AH34" s="0" t="n">
+        <v>0.038569</v>
+      </c>
+      <c r="AI34" s="1" t="n">
         <v>0.462158029165236</v>
       </c>
-      <c r="AH34" s="0" t="n">
+      <c r="AJ34" s="1" t="n">
         <v>0.462158029165236</v>
       </c>
-      <c r="AI34" s="0" t="n">
+      <c r="AK34" s="1" t="n">
         <v>0.462158029165236</v>
       </c>
-      <c r="AJ34" s="0" t="n">
+      <c r="AL34" s="1" t="n">
         <v>0.462158029165236</v>
       </c>
-      <c r="AK34" s="0" t="n">
-        <v>0.462158029165236</v>
-      </c>
-      <c r="AL34" s="0" t="n">
-        <v>0.462158029165236</v>
-      </c>
-      <c r="AO34" s="0" t="s">
+      <c r="AO34" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW34" s="0" t="n">
-        <v>0.462158029165236</v>
+        <v>0.038569</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="D35" s="1" t="n">
+      <c r="D35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="F35" s="1" t="n">
+      <c r="F35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="G35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="H35" s="1" t="n">
+      <c r="H35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="I35" s="1" t="n">
+      <c r="I35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="K35" s="0" t="n">
+      <c r="K35" s="1" t="n">
         <v>0.640908813154522</v>
       </c>
-      <c r="L35" s="0" t="n">
+      <c r="L35" s="1" t="n">
         <v>0.640908813154522</v>
       </c>
-      <c r="M35" s="0" t="n">
+      <c r="M35" s="1" t="n">
         <v>0.640908813154522</v>
       </c>
-      <c r="N35" s="0" t="n">
+      <c r="N35" s="1" t="n">
         <v>0.640908813154522</v>
       </c>
-      <c r="R35" s="0" t="n">
+      <c r="R35" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S35" s="0" t="n">
+      <c r="S35" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T35" s="0" t="s">
+      <c r="T35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U35" s="1" t="n">
+      <c r="U35" s="2" t="n">
         <v>188.417675132124</v>
       </c>
-      <c r="V35" s="0" t="n">
+      <c r="V35" s="1" t="n">
         <v>0.470843827165367</v>
       </c>
-      <c r="W35" s="1" t="n">
-        <v>1620334825.81708</v>
-      </c>
-      <c r="X35" s="0" t="n">
+      <c r="W35" s="2" t="n">
+        <v>712450</v>
+      </c>
+      <c r="X35" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y35" s="0" t="s">
+      <c r="Y35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="Z35" s="0" t="s">
+      <c r="Z35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AA35" s="1" t="n">
+      <c r="AA35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
-      <c r="AB35" s="1" t="n">
+      <c r="AB35" s="2" t="n">
         <v>837946302.443684</v>
       </c>
       <c r="AC35" s="0" t="n">
-        <v>0.555749741891446</v>
+        <v>0.043233</v>
       </c>
       <c r="AD35" s="0" t="n">
-        <v>0.555749741891446</v>
+        <v>0.043233</v>
       </c>
       <c r="AE35" s="0" t="n">
-        <v>0.555749741891446</v>
+        <v>0.043233</v>
       </c>
       <c r="AF35" s="0" t="n">
-        <v>0.555749741891446</v>
+        <v>0.043233</v>
       </c>
       <c r="AG35" s="0" t="n">
+        <v>0.043233</v>
+      </c>
+      <c r="AH35" s="0" t="n">
+        <v>0.043233</v>
+      </c>
+      <c r="AI35" s="1" t="n">
         <v>0.470843827165367</v>
       </c>
-      <c r="AH35" s="0" t="n">
+      <c r="AJ35" s="1" t="n">
         <v>0.470843827165367</v>
       </c>
-      <c r="AI35" s="0" t="n">
+      <c r="AK35" s="1" t="n">
         <v>0.470843827165367</v>
       </c>
-      <c r="AJ35" s="0" t="n">
+      <c r="AL35" s="1" t="n">
         <v>0.470843827165367</v>
       </c>
-      <c r="AK35" s="0" t="n">
-        <v>0.470843827165367</v>
-      </c>
-      <c r="AL35" s="0" t="n">
-        <v>0.470843827165367</v>
-      </c>
-      <c r="AO35" s="0" t="s">
+      <c r="AO35" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW35" s="0" t="n">
-        <v>0.470843827165367</v>
+        <v>0.043233</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>181</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="D36" s="1" t="n">
+      <c r="D36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="F36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="G36" s="1" t="n">
+      <c r="G36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="H36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="I36" s="1" t="n">
+      <c r="I36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="K36" s="0" t="n">
+      <c r="K36" s="1" t="n">
         <v>0.652414408168272</v>
       </c>
-      <c r="L36" s="0" t="n">
+      <c r="L36" s="1" t="n">
         <v>0.652414408168272</v>
       </c>
-      <c r="M36" s="0" t="n">
+      <c r="M36" s="1" t="n">
         <v>0.652414408168272</v>
       </c>
-      <c r="N36" s="0" t="n">
+      <c r="N36" s="1" t="n">
         <v>0.652414408168272</v>
       </c>
-      <c r="R36" s="0" t="n">
+      <c r="R36" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S36" s="0" t="n">
+      <c r="S36" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T36" s="0" t="s">
+      <c r="T36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U36" s="1" t="n">
+      <c r="U36" s="2" t="n">
         <v>195.914814425632</v>
       </c>
-      <c r="V36" s="0" t="n">
+      <c r="V36" s="1" t="n">
         <v>0.479692866053113</v>
       </c>
-      <c r="W36" s="1" t="n">
-        <v>1695037754.2223</v>
-      </c>
-      <c r="X36" s="0" t="n">
+      <c r="W36" s="2" t="n">
+        <v>978780</v>
+      </c>
+      <c r="X36" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y36" s="0" t="s">
+      <c r="Y36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Z36" s="0" t="s">
+      <c r="Z36" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AA36" s="1" t="n">
+      <c r="AA36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
-      <c r="AB36" s="1" t="n">
+      <c r="AB36" s="2" t="n">
         <v>892009759.931048</v>
       </c>
       <c r="AC36" s="0" t="n">
-        <v>0.568962136255173</v>
+        <v>0.04846</v>
       </c>
       <c r="AD36" s="0" t="n">
-        <v>0.568962136255173</v>
+        <v>0.04846</v>
       </c>
       <c r="AE36" s="0" t="n">
-        <v>0.568962136255173</v>
+        <v>0.04846</v>
       </c>
       <c r="AF36" s="0" t="n">
-        <v>0.568962136255173</v>
+        <v>0.04846</v>
       </c>
       <c r="AG36" s="0" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="AH36" s="0" t="n">
+        <v>0.04846</v>
+      </c>
+      <c r="AI36" s="1" t="n">
         <v>0.479692866053113</v>
       </c>
-      <c r="AH36" s="0" t="n">
+      <c r="AJ36" s="1" t="n">
         <v>0.479692866053113</v>
       </c>
-      <c r="AI36" s="0" t="n">
+      <c r="AK36" s="1" t="n">
         <v>0.479692866053113</v>
       </c>
-      <c r="AJ36" s="0" t="n">
+      <c r="AL36" s="1" t="n">
         <v>0.479692866053113</v>
       </c>
-      <c r="AK36" s="0" t="n">
-        <v>0.479692866053113</v>
-      </c>
-      <c r="AL36" s="0" t="n">
-        <v>0.479692866053113</v>
-      </c>
-      <c r="AO36" s="0" t="s">
+      <c r="AO36" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW36" s="0" t="n">
-        <v>0.479692866053113</v>
+        <v>0.04846</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="1" t="n">
         <v>182</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="D37" s="1" t="n">
+      <c r="D37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="F37" s="1" t="n">
+      <c r="F37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="G37" s="1" t="n">
+      <c r="G37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="H37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="I37" s="1" t="n">
+      <c r="I37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="K37" s="0" t="n">
+      <c r="K37" s="1" t="n">
         <v>0.664126551623709</v>
       </c>
-      <c r="L37" s="0" t="n">
+      <c r="L37" s="1" t="n">
         <v>0.664126551623709</v>
       </c>
-      <c r="M37" s="0" t="n">
+      <c r="M37" s="1" t="n">
         <v>0.664126551623709</v>
       </c>
-      <c r="N37" s="0" t="n">
+      <c r="N37" s="1" t="n">
         <v>0.664126551623709</v>
       </c>
-      <c r="P37" s="0" t="n">
+      <c r="P37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="0" t="n">
+      <c r="Q37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="R37" s="0" t="n">
+      <c r="R37" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S37" s="0" t="n">
+      <c r="S37" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T37" s="0" t="s">
+      <c r="T37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U37" s="1" t="n">
+      <c r="U37" s="2" t="n">
         <v>203.710264891628</v>
       </c>
-      <c r="V37" s="0" t="n">
+      <c r="V37" s="1" t="n">
         <v>0.488708213777715</v>
       </c>
-      <c r="W37" s="1" t="n">
-        <v>1773184740.86994</v>
-      </c>
-      <c r="X37" s="0" t="n">
+      <c r="W37" s="2" t="n">
+        <v>1344671</v>
+      </c>
+      <c r="X37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y37" s="0" t="s">
+      <c r="Y37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="Z37" s="0" t="s">
+      <c r="Z37" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="AA37" s="1" t="n">
+      <c r="AA37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
-      <c r="AB37" s="1" t="n">
+      <c r="AB37" s="2" t="n">
         <v>949561337.63204</v>
       </c>
       <c r="AC37" s="0" t="n">
-        <v>0.582488642082504</v>
+        <v>0.054319</v>
       </c>
       <c r="AD37" s="0" t="n">
-        <v>0.582488642082504</v>
+        <v>0.054319</v>
       </c>
       <c r="AE37" s="0" t="n">
-        <v>0.582488642082504</v>
+        <v>0.054319</v>
       </c>
       <c r="AF37" s="0" t="n">
-        <v>0.582488642082504</v>
+        <v>0.054319</v>
       </c>
       <c r="AG37" s="0" t="n">
+        <v>0.054319</v>
+      </c>
+      <c r="AH37" s="0" t="n">
+        <v>0.054319</v>
+      </c>
+      <c r="AI37" s="1" t="n">
         <v>0.488708213777715</v>
       </c>
-      <c r="AH37" s="0" t="n">
+      <c r="AJ37" s="1" t="n">
         <v>0.488708213777715</v>
       </c>
-      <c r="AI37" s="0" t="n">
+      <c r="AK37" s="1" t="n">
         <v>0.488708213777715</v>
       </c>
-      <c r="AJ37" s="0" t="n">
+      <c r="AL37" s="1" t="n">
         <v>0.488708213777715</v>
       </c>
-      <c r="AK37" s="0" t="n">
-        <v>0.488708213777715</v>
-      </c>
-      <c r="AL37" s="0" t="n">
-        <v>0.488708213777715</v>
-      </c>
-      <c r="AN37" s="0" t="n">
+      <c r="AN37" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="AO37" s="0" t="s">
+      <c r="AO37" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW37" s="0" t="n">
-        <v>0.488708213777715</v>
+        <v>0.054319</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>183</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="D38" s="1" t="n">
+      <c r="D38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="G38" s="1" t="n">
+      <c r="G38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="H38" s="1" t="n">
+      <c r="H38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="I38" s="1" t="n">
+      <c r="I38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="K38" s="0" t="n">
+      <c r="K38" s="1" t="n">
         <v>0.676048951478458</v>
       </c>
-      <c r="L38" s="0" t="n">
+      <c r="L38" s="1" t="n">
         <v>0.676048951478458</v>
       </c>
-      <c r="M38" s="0" t="n">
+      <c r="M38" s="1" t="n">
         <v>0.676048951478458</v>
       </c>
-      <c r="N38" s="0" t="n">
+      <c r="N38" s="1" t="n">
         <v>0.676048951478458</v>
       </c>
-      <c r="R38" s="0" t="n">
+      <c r="R38" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S38" s="0" t="n">
+      <c r="S38" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T38" s="0" t="s">
+      <c r="T38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U38" s="1" t="n">
+      <c r="U38" s="2" t="n">
         <v>211.815896331665</v>
       </c>
-      <c r="V38" s="0" t="n">
+      <c r="V38" s="1" t="n">
         <v>0.497892995947453</v>
       </c>
-      <c r="W38" s="1" t="n">
-        <v>1854934568.52031</v>
-      </c>
-      <c r="X38" s="0" t="n">
+      <c r="W38" s="2" t="n">
+        <v>1847342</v>
+      </c>
+      <c r="X38" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y38" s="0" t="s">
+      <c r="Y38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Z38" s="0" t="s">
+      <c r="Z38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="AA38" s="1" t="n">
+      <c r="AA38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
-      <c r="AB38" s="1" t="n">
+      <c r="AB38" s="2" t="n">
         <v>1010826085.57472</v>
       </c>
       <c r="AC38" s="0" t="n">
-        <v>0.596336727059373</v>
+        <v>0.060886</v>
       </c>
       <c r="AD38" s="0" t="n">
-        <v>0.596336727059373</v>
+        <v>0.060886</v>
       </c>
       <c r="AE38" s="0" t="n">
-        <v>0.596336727059373</v>
+        <v>0.060886</v>
       </c>
       <c r="AF38" s="0" t="n">
-        <v>0.596336727059373</v>
+        <v>0.060886</v>
       </c>
       <c r="AG38" s="0" t="n">
+        <v>0.060886</v>
+      </c>
+      <c r="AH38" s="0" t="n">
+        <v>0.060886</v>
+      </c>
+      <c r="AI38" s="1" t="n">
         <v>0.497892995947453</v>
       </c>
-      <c r="AH38" s="0" t="n">
+      <c r="AJ38" s="1" t="n">
         <v>0.497892995947453</v>
       </c>
-      <c r="AI38" s="0" t="n">
+      <c r="AK38" s="1" t="n">
         <v>0.497892995947453</v>
       </c>
-      <c r="AJ38" s="0" t="n">
+      <c r="AL38" s="1" t="n">
         <v>0.497892995947453</v>
       </c>
-      <c r="AK38" s="0" t="n">
-        <v>0.497892995947453</v>
-      </c>
-      <c r="AL38" s="0" t="n">
-        <v>0.497892995947453</v>
-      </c>
-      <c r="AO38" s="0" t="s">
+      <c r="AO38" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW38" s="0" t="n">
-        <v>0.497892995947453</v>
+        <v>0.060886</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>184</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="D39" s="1" t="n">
+      <c r="D39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="F39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="G39" s="1" t="n">
+      <c r="G39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="I39" s="1" t="n">
+      <c r="I39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="K39" s="0" t="n">
+      <c r="K39" s="1" t="n">
         <v>0.688185382255399</v>
       </c>
-      <c r="L39" s="0" t="n">
+      <c r="L39" s="1" t="n">
         <v>0.688185382255399</v>
       </c>
-      <c r="M39" s="0" t="n">
+      <c r="M39" s="1" t="n">
         <v>0.688185382255399</v>
       </c>
-      <c r="N39" s="0" t="n">
+      <c r="N39" s="1" t="n">
         <v>0.688185382255399</v>
       </c>
-      <c r="R39" s="0" t="n">
+      <c r="R39" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S39" s="0" t="n">
+      <c r="S39" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T39" s="0" t="s">
+      <c r="T39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U39" s="1" t="n">
+      <c r="U39" s="2" t="n">
         <v>220.244050846702</v>
       </c>
-      <c r="V39" s="0" t="n">
+      <c r="V39" s="1" t="n">
         <v>0.50725039691329</v>
       </c>
-      <c r="W39" s="1" t="n">
-        <v>1940453340.35729</v>
-      </c>
-      <c r="X39" s="0" t="n">
+      <c r="W39" s="2" t="n">
+        <v>2537922</v>
+      </c>
+      <c r="X39" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y39" s="0" t="s">
+      <c r="Y39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="Z39" s="0" t="s">
+      <c r="Z39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="AA39" s="1" t="n">
+      <c r="AA39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
-      <c r="AB39" s="1" t="n">
+      <c r="AB39" s="2" t="n">
         <v>1076043573.78992</v>
       </c>
       <c r="AC39" s="0" t="n">
-        <v>0.610514036408483</v>
+        <v>0.068248</v>
       </c>
       <c r="AD39" s="0" t="n">
-        <v>0.610514036408483</v>
+        <v>0.068248</v>
       </c>
       <c r="AE39" s="0" t="n">
-        <v>0.610514036408483</v>
+        <v>0.068248</v>
       </c>
       <c r="AF39" s="0" t="n">
-        <v>0.610514036408483</v>
+        <v>0.068248</v>
       </c>
       <c r="AG39" s="0" t="n">
+        <v>0.068248</v>
+      </c>
+      <c r="AH39" s="0" t="n">
+        <v>0.068248</v>
+      </c>
+      <c r="AI39" s="1" t="n">
         <v>0.50725039691329</v>
       </c>
-      <c r="AH39" s="0" t="n">
+      <c r="AJ39" s="1" t="n">
         <v>0.50725039691329</v>
       </c>
-      <c r="AI39" s="0" t="n">
+      <c r="AK39" s="1" t="n">
         <v>0.50725039691329</v>
       </c>
-      <c r="AJ39" s="0" t="n">
+      <c r="AL39" s="1" t="n">
         <v>0.50725039691329</v>
       </c>
-      <c r="AK39" s="0" t="n">
-        <v>0.50725039691329</v>
-      </c>
-      <c r="AL39" s="0" t="n">
-        <v>0.50725039691329</v>
-      </c>
-      <c r="AO39" s="0" t="s">
+      <c r="AO39" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW39" s="0" t="n">
-        <v>0.50725039691329</v>
+        <v>0.068248</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="1" t="n">
         <v>185</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="D40" s="1" t="n">
+      <c r="D40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="F40" s="1" t="n">
+      <c r="F40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="G40" s="1" t="n">
+      <c r="G40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="I40" s="1" t="n">
+      <c r="I40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="K40" s="0" t="n">
+      <c r="K40" s="1" t="n">
         <v>0.700539686237648</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="1" t="n">
         <v>0.700539686237648</v>
       </c>
-      <c r="M40" s="0" t="n">
+      <c r="M40" s="1" t="n">
         <v>0.700539686237648</v>
       </c>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="1" t="n">
         <v>0.700539686237648</v>
       </c>
-      <c r="R40" s="0" t="n">
+      <c r="R40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S40" s="0" t="n">
+      <c r="S40" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T40" s="0" t="s">
+      <c r="T40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U40" s="1" t="n">
+      <c r="U40" s="2" t="n">
         <v>229.007561629893</v>
       </c>
-      <c r="V40" s="0" t="n">
+      <c r="V40" s="1" t="n">
         <v>0.516783660872878</v>
       </c>
-      <c r="W40" s="1" t="n">
-        <v>2029914817.48458</v>
-      </c>
-      <c r="X40" s="0" t="n">
+      <c r="W40" s="2" t="n">
+        <v>3486658</v>
+      </c>
+      <c r="X40" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y40" s="0" t="s">
+      <c r="Y40" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Z40" s="0" t="s">
+      <c r="Z40" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AA40" s="1" t="n">
+      <c r="AA40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
-      <c r="AB40" s="1" t="n">
+      <c r="AB40" s="2" t="n">
         <v>1145468829.12727</v>
       </c>
       <c r="AC40" s="0" t="n">
-        <v>0.625028397110058</v>
+        <v>0.0765</v>
       </c>
       <c r="AD40" s="0" t="n">
-        <v>0.625028397110058</v>
+        <v>0.0765</v>
       </c>
       <c r="AE40" s="0" t="n">
-        <v>0.625028397110058</v>
+        <v>0.0765</v>
       </c>
       <c r="AF40" s="0" t="n">
-        <v>0.625028397110058</v>
+        <v>0.0765</v>
       </c>
       <c r="AG40" s="0" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="AH40" s="0" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="AI40" s="1" t="n">
         <v>0.516783660872878</v>
       </c>
-      <c r="AH40" s="0" t="n">
+      <c r="AJ40" s="1" t="n">
         <v>0.516783660872878</v>
       </c>
-      <c r="AI40" s="0" t="n">
+      <c r="AK40" s="1" t="n">
         <v>0.516783660872878</v>
       </c>
-      <c r="AJ40" s="0" t="n">
+      <c r="AL40" s="1" t="n">
         <v>0.516783660872878</v>
       </c>
-      <c r="AK40" s="0" t="n">
-        <v>0.516783660872878</v>
-      </c>
-      <c r="AL40" s="0" t="n">
-        <v>0.516783660872878</v>
-      </c>
-      <c r="AO40" s="0" t="s">
+      <c r="AO40" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW40" s="0" t="n">
-        <v>0.516783660872878</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="1" t="n">
         <v>186</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="D41" s="1" t="n">
+      <c r="D41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="F41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="G41" s="1" t="n">
+      <c r="G41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="I41" s="1" t="n">
+      <c r="I41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="K41" s="0" t="n">
+      <c r="K41" s="1" t="n">
         <v>0.713115774684986</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="1" t="n">
         <v>0.713115774684986</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="1" t="n">
         <v>0.713115774684986</v>
       </c>
-      <c r="N41" s="0" t="n">
+      <c r="N41" s="1" t="n">
         <v>0.713115774684986</v>
       </c>
-      <c r="R41" s="0" t="n">
+      <c r="R41" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S41" s="0" t="n">
+      <c r="S41" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T41" s="0" t="s">
+      <c r="T41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U41" s="1" t="n">
+      <c r="U41" s="2" t="n">
         <v>238.119772507146</v>
       </c>
-      <c r="V41" s="0" t="n">
+      <c r="V41" s="1" t="n">
         <v>0.526496092995323</v>
       </c>
-      <c r="W41" s="1" t="n">
-        <v>2123500771.98185</v>
-      </c>
-      <c r="X41" s="0" t="n">
+      <c r="W41" s="2" t="n">
+        <v>4790053</v>
+      </c>
+      <c r="X41" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y41" s="0" t="s">
+      <c r="Y41" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="Z41" s="0" t="s">
+      <c r="Z41" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AA41" s="1" t="n">
+      <c r="AA41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
-      <c r="AB41" s="1" t="n">
+      <c r="AB41" s="2" t="n">
         <v>1219373332.51373</v>
       </c>
       <c r="AC41" s="0" t="n">
-        <v>0.639887822222953</v>
+        <v>0.085749</v>
       </c>
       <c r="AD41" s="0" t="n">
-        <v>0.639887822222953</v>
+        <v>0.085749</v>
       </c>
       <c r="AE41" s="0" t="n">
-        <v>0.639887822222953</v>
+        <v>0.085749</v>
       </c>
       <c r="AF41" s="0" t="n">
-        <v>0.639887822222953</v>
+        <v>0.085749</v>
       </c>
       <c r="AG41" s="0" t="n">
+        <v>0.085749</v>
+      </c>
+      <c r="AH41" s="0" t="n">
+        <v>0.085749</v>
+      </c>
+      <c r="AI41" s="1" t="n">
         <v>0.526496092995323</v>
       </c>
-      <c r="AH41" s="0" t="n">
+      <c r="AJ41" s="1" t="n">
         <v>0.526496092995323</v>
       </c>
-      <c r="AI41" s="0" t="n">
+      <c r="AK41" s="1" t="n">
         <v>0.526496092995323</v>
       </c>
-      <c r="AJ41" s="0" t="n">
+      <c r="AL41" s="1" t="n">
         <v>0.526496092995323</v>
       </c>
-      <c r="AK41" s="0" t="n">
-        <v>0.526496092995323</v>
-      </c>
-      <c r="AL41" s="0" t="n">
-        <v>0.526496092995323</v>
-      </c>
-      <c r="AO41" s="0" t="s">
+      <c r="AO41" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW41" s="0" t="n">
-        <v>0.526496092995323</v>
+        <v>0.085749</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="1" t="n">
         <v>187</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="F42" s="1" t="n">
+      <c r="F42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="G42" s="1" t="n">
+      <c r="G42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="H42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="I42" s="1" t="n">
+      <c r="I42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="K42" s="0" t="n">
+      <c r="K42" s="1" t="n">
         <v>0.725917629072131</v>
       </c>
-      <c r="L42" s="0" t="n">
+      <c r="L42" s="1" t="n">
         <v>0.725917629072131</v>
       </c>
-      <c r="M42" s="0" t="n">
+      <c r="M42" s="1" t="n">
         <v>0.725917629072131</v>
       </c>
-      <c r="N42" s="0" t="n">
+      <c r="N42" s="1" t="n">
         <v>0.725917629072131</v>
       </c>
-      <c r="R42" s="0" t="n">
+      <c r="R42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S42" s="0" t="n">
+      <c r="S42" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T42" s="0" t="s">
+      <c r="T42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U42" s="1" t="n">
+      <c r="U42" s="2" t="n">
         <v>247.594558255205</v>
       </c>
-      <c r="V42" s="0" t="n">
+      <c r="V42" s="1" t="n">
         <v>0.536391060567077</v>
       </c>
-      <c r="W42" s="1" t="n">
-        <v>2221401356.23783</v>
-      </c>
-      <c r="X42" s="0" t="n">
+      <c r="W42" s="2" t="n">
+        <v>6580689</v>
+      </c>
+      <c r="X42" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y42" s="0" t="s">
+      <c r="Y42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="Z42" s="0" t="s">
+      <c r="Z42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AA42" s="1" t="n">
+      <c r="AA42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
-      <c r="AB42" s="1" t="n">
+      <c r="AB42" s="2" t="n">
         <v>1298046080.55418</v>
       </c>
       <c r="AC42" s="0" t="n">
-        <v>0.655100515308481</v>
+        <v>0.096117</v>
       </c>
       <c r="AD42" s="0" t="n">
-        <v>0.655100515308481</v>
+        <v>0.096117</v>
       </c>
       <c r="AE42" s="0" t="n">
-        <v>0.655100515308481</v>
+        <v>0.096117</v>
       </c>
       <c r="AF42" s="0" t="n">
-        <v>0.655100515308481</v>
+        <v>0.096117</v>
       </c>
       <c r="AG42" s="0" t="n">
+        <v>0.096117</v>
+      </c>
+      <c r="AH42" s="0" t="n">
+        <v>0.096117</v>
+      </c>
+      <c r="AI42" s="1" t="n">
         <v>0.536391060567077</v>
       </c>
-      <c r="AH42" s="0" t="n">
+      <c r="AJ42" s="1" t="n">
         <v>0.536391060567077</v>
       </c>
-      <c r="AI42" s="0" t="n">
+      <c r="AK42" s="1" t="n">
         <v>0.536391060567077</v>
       </c>
-      <c r="AJ42" s="0" t="n">
+      <c r="AL42" s="1" t="n">
         <v>0.536391060567077</v>
       </c>
-      <c r="AK42" s="0" t="n">
-        <v>0.536391060567077</v>
-      </c>
-      <c r="AL42" s="0" t="n">
-        <v>0.536391060567077</v>
-      </c>
-      <c r="AO42" s="0" t="s">
+      <c r="AO42" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW42" s="0" t="n">
-        <v>0.536391060567077</v>
+        <v>0.096117</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="1" t="n">
         <v>188</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="F43" s="1" t="n">
+      <c r="F43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="G43" s="1" t="n">
+      <c r="G43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="H43" s="1" t="n">
+      <c r="H43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="I43" s="1" t="n">
+      <c r="I43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="K43" s="0" t="n">
+      <c r="K43" s="1" t="n">
         <v>0.738949302349234</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="1" t="n">
         <v>0.738949302349234</v>
       </c>
-      <c r="M43" s="0" t="n">
+      <c r="M43" s="1" t="n">
         <v>0.738949302349234</v>
       </c>
-      <c r="N43" s="0" t="n">
+      <c r="N43" s="1" t="n">
         <v>0.738949302349234</v>
       </c>
-      <c r="R43" s="0" t="n">
+      <c r="R43" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S43" s="0" t="n">
+      <c r="S43" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T43" s="0" t="s">
+      <c r="T43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="1" t="n">
+      <c r="U43" s="2" t="n">
         <v>257.44634572818</v>
       </c>
-      <c r="V43" s="0" t="n">
+      <c r="V43" s="1" t="n">
         <v>0.546471994159375</v>
       </c>
-      <c r="W43" s="1" t="n">
-        <v>2323815489.31099</v>
-      </c>
-      <c r="X43" s="0" t="n">
+      <c r="W43" s="2" t="n">
+        <v>9040707</v>
+      </c>
+      <c r="X43" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y43" s="0" t="s">
+      <c r="Y43" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="Z43" s="0" t="s">
+      <c r="Z43" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AA43" s="1" t="n">
+      <c r="AA43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
-      <c r="AB43" s="1" t="n">
+      <c r="AB43" s="2" t="n">
         <v>1381794715.62546</v>
       </c>
       <c r="AC43" s="0" t="n">
-        <v>0.670674874959425</v>
+        <v>0.107738</v>
       </c>
       <c r="AD43" s="0" t="n">
-        <v>0.670674874959425</v>
+        <v>0.107738</v>
       </c>
       <c r="AE43" s="0" t="n">
-        <v>0.670674874959425</v>
+        <v>0.107738</v>
       </c>
       <c r="AF43" s="0" t="n">
-        <v>0.670674874959425</v>
+        <v>0.107738</v>
       </c>
       <c r="AG43" s="0" t="n">
+        <v>0.107738</v>
+      </c>
+      <c r="AH43" s="0" t="n">
+        <v>0.107738</v>
+      </c>
+      <c r="AI43" s="1" t="n">
         <v>0.546471994159375</v>
       </c>
-      <c r="AH43" s="0" t="n">
+      <c r="AJ43" s="1" t="n">
         <v>0.546471994159375</v>
       </c>
-      <c r="AI43" s="0" t="n">
+      <c r="AK43" s="1" t="n">
         <v>0.546471994159375</v>
       </c>
-      <c r="AJ43" s="0" t="n">
+      <c r="AL43" s="1" t="n">
         <v>0.546471994159375</v>
       </c>
-      <c r="AK43" s="0" t="n">
-        <v>0.546471994159375</v>
-      </c>
-      <c r="AL43" s="0" t="n">
-        <v>0.546471994159375</v>
-      </c>
-      <c r="AO43" s="0" t="s">
+      <c r="AO43" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW43" s="0" t="n">
-        <v>0.546471994159375</v>
+        <v>0.107738</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="1" t="n">
         <v>189</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="F44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="G44" s="1" t="n">
+      <c r="G44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="H44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="I44" s="1" t="n">
+      <c r="I44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="K44" s="0" t="n">
+      <c r="K44" s="1" t="n">
         <v>0.752214920225007</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="1" t="n">
         <v>0.752214920225007</v>
       </c>
-      <c r="M44" s="0" t="n">
+      <c r="M44" s="1" t="n">
         <v>0.752214920225007</v>
       </c>
-      <c r="N44" s="0" t="n">
+      <c r="N44" s="1" t="n">
         <v>0.752214920225007</v>
       </c>
-      <c r="R44" s="0" t="n">
+      <c r="R44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S44" s="0" t="n">
+      <c r="S44" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T44" s="0" t="s">
+      <c r="T44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U44" s="1" t="n">
+      <c r="U44" s="2" t="n">
         <v>267.690135824704</v>
       </c>
-      <c r="V44" s="0" t="n">
+      <c r="V44" s="1" t="n">
         <v>0.556742388817606</v>
       </c>
-      <c r="W44" s="1" t="n">
-        <v>2430951261.10274</v>
-      </c>
-      <c r="X44" s="0" t="n">
+      <c r="W44" s="2" t="n">
+        <v>12420339</v>
+      </c>
+      <c r="X44" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y44" s="0" t="s">
+      <c r="Y44" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="Z44" s="0" t="s">
+      <c r="Z44" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="AA44" s="1" t="n">
+      <c r="AA44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
-      <c r="AB44" s="1" t="n">
+      <c r="AB44" s="2" t="n">
         <v>1470946728.8829</v>
       </c>
       <c r="AC44" s="0" t="n">
-        <v>0.68661949943671</v>
+        <v>0.120765</v>
       </c>
       <c r="AD44" s="0" t="n">
-        <v>0.68661949943671</v>
+        <v>0.120765</v>
       </c>
       <c r="AE44" s="0" t="n">
-        <v>0.68661949943671</v>
+        <v>0.120765</v>
       </c>
       <c r="AF44" s="0" t="n">
-        <v>0.68661949943671</v>
+        <v>0.120765</v>
       </c>
       <c r="AG44" s="0" t="n">
+        <v>0.120765</v>
+      </c>
+      <c r="AH44" s="0" t="n">
+        <v>0.120765</v>
+      </c>
+      <c r="AI44" s="1" t="n">
         <v>0.556742388817606</v>
       </c>
-      <c r="AH44" s="0" t="n">
+      <c r="AJ44" s="1" t="n">
         <v>0.556742388817606</v>
       </c>
-      <c r="AI44" s="0" t="n">
+      <c r="AK44" s="1" t="n">
         <v>0.556742388817606</v>
       </c>
-      <c r="AJ44" s="0" t="n">
+      <c r="AL44" s="1" t="n">
         <v>0.556742388817606</v>
       </c>
-      <c r="AK44" s="0" t="n">
-        <v>0.556742388817606</v>
-      </c>
-      <c r="AL44" s="0" t="n">
-        <v>0.556742388817606</v>
-      </c>
-      <c r="AO44" s="0" t="s">
+      <c r="AO44" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW44" s="0" t="n">
-        <v>0.556742388817606</v>
+        <v>0.120765</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="1" t="n">
         <v>190</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="F45" s="1" t="n">
+      <c r="F45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="G45" s="1" t="n">
+      <c r="G45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="H45" s="1" t="n">
+      <c r="H45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="I45" s="1" t="n">
+      <c r="I45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="K45" s="0" t="n">
+      <c r="K45" s="1" t="n">
         <v>0.765718682472886</v>
       </c>
-      <c r="L45" s="0" t="n">
+      <c r="L45" s="1" t="n">
         <v>0.765718682472886</v>
       </c>
-      <c r="M45" s="0" t="n">
+      <c r="M45" s="1" t="n">
         <v>0.765718682472886</v>
       </c>
-      <c r="N45" s="0" t="n">
+      <c r="N45" s="1" t="n">
         <v>0.765718682472886</v>
       </c>
-      <c r="R45" s="0" t="n">
+      <c r="R45" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S45" s="0" t="n">
+      <c r="S45" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T45" s="0" t="s">
+      <c r="T45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U45" s="1" t="n">
+      <c r="U45" s="2" t="n">
         <v>278.341526329169</v>
       </c>
-      <c r="V45" s="0" t="n">
+      <c r="V45" s="1" t="n">
         <v>0.567205805273044</v>
       </c>
-      <c r="W45" s="1" t="n">
-        <v>2543026355.16435</v>
-      </c>
-      <c r="X45" s="0" t="n">
+      <c r="W45" s="2" t="n">
+        <v>17063357</v>
+      </c>
+      <c r="X45" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y45" s="0" t="s">
+      <c r="Y45" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="Z45" s="0" t="s">
+      <c r="Z45" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AA45" s="1" t="n">
+      <c r="AA45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
-      <c r="AB45" s="1" t="n">
+      <c r="AB45" s="2" t="n">
         <v>1565850740.88369</v>
       </c>
       <c r="AC45" s="0" t="n">
-        <v>0.702943191416319</v>
+        <v>0.135366</v>
       </c>
       <c r="AD45" s="0" t="n">
-        <v>0.702943191416319</v>
+        <v>0.135366</v>
       </c>
       <c r="AE45" s="0" t="n">
-        <v>0.702943191416319</v>
+        <v>0.135366</v>
       </c>
       <c r="AF45" s="0" t="n">
-        <v>0.702943191416319</v>
+        <v>0.135366</v>
       </c>
       <c r="AG45" s="0" t="n">
+        <v>0.135366</v>
+      </c>
+      <c r="AH45" s="0" t="n">
+        <v>0.135366</v>
+      </c>
+      <c r="AI45" s="1" t="n">
         <v>0.567205805273044</v>
       </c>
-      <c r="AH45" s="0" t="n">
+      <c r="AJ45" s="1" t="n">
         <v>0.567205805273044</v>
       </c>
-      <c r="AI45" s="0" t="n">
+      <c r="AK45" s="1" t="n">
         <v>0.567205805273044</v>
       </c>
-      <c r="AJ45" s="0" t="n">
+      <c r="AL45" s="1" t="n">
         <v>0.567205805273044</v>
       </c>
-      <c r="AK45" s="0" t="n">
-        <v>0.567205805273044</v>
-      </c>
-      <c r="AL45" s="0" t="n">
-        <v>0.567205805273044</v>
-      </c>
-      <c r="AO45" s="0" t="s">
+      <c r="AO45" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW45" s="0" t="n">
-        <v>0.567205805273044</v>
+        <v>0.135366</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="1" t="n">
         <v>191</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="D46" s="1" t="n">
+      <c r="D46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="G46" s="1" t="n">
+      <c r="G46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="H46" s="1" t="n">
+      <c r="H46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="I46" s="1" t="n">
+      <c r="I46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="K46" s="0" t="n">
+      <c r="K46" s="1" t="n">
         <v>0.77946486426064</v>
       </c>
-      <c r="L46" s="0" t="n">
+      <c r="L46" s="1" t="n">
         <v>0.77946486426064</v>
       </c>
-      <c r="M46" s="0" t="n">
+      <c r="M46" s="1" t="n">
         <v>0.77946486426064</v>
       </c>
-      <c r="N46" s="0" t="n">
+      <c r="N46" s="1" t="n">
         <v>0.77946486426064</v>
       </c>
-      <c r="R46" s="0" t="n">
+      <c r="R46" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S46" s="0" t="n">
+      <c r="S46" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T46" s="0" t="s">
+      <c r="T46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U46" s="1" t="n">
+      <c r="U46" s="2" t="n">
         <v>289.416735661807</v>
       </c>
-      <c r="V46" s="0" t="n">
+      <c r="V46" s="1" t="n">
         <v>0.577865871177346</v>
       </c>
-      <c r="W46" s="1" t="n">
-        <v>2660268490.99677</v>
-      </c>
-      <c r="X46" s="0" t="n">
+      <c r="W46" s="2" t="n">
+        <v>23442045</v>
+      </c>
+      <c r="X46" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y46" s="0" t="s">
+      <c r="Y46" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Z46" s="0" t="s">
+      <c r="Z46" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AA46" s="1" t="n">
+      <c r="AA46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
-      <c r="AB46" s="1" t="n">
+      <c r="AB46" s="2" t="n">
         <v>1666877864.83477</v>
       </c>
       <c r="AC46" s="0" t="n">
-        <v>0.71965496284905</v>
+        <v>0.151733</v>
       </c>
       <c r="AD46" s="0" t="n">
-        <v>0.71965496284905</v>
+        <v>0.151733</v>
       </c>
       <c r="AE46" s="0" t="n">
-        <v>0.71965496284905</v>
+        <v>0.151733</v>
       </c>
       <c r="AF46" s="0" t="n">
-        <v>0.71965496284905</v>
+        <v>0.151733</v>
       </c>
       <c r="AG46" s="0" t="n">
+        <v>0.151733</v>
+      </c>
+      <c r="AH46" s="0" t="n">
+        <v>0.151733</v>
+      </c>
+      <c r="AI46" s="1" t="n">
         <v>0.577865871177346</v>
       </c>
-      <c r="AH46" s="0" t="n">
+      <c r="AJ46" s="1" t="n">
         <v>0.577865871177346</v>
       </c>
-      <c r="AI46" s="0" t="n">
+      <c r="AK46" s="1" t="n">
         <v>0.577865871177346</v>
       </c>
-      <c r="AJ46" s="0" t="n">
+      <c r="AL46" s="1" t="n">
         <v>0.577865871177346</v>
       </c>
-      <c r="AK46" s="0" t="n">
-        <v>0.577865871177346</v>
-      </c>
-      <c r="AL46" s="0" t="n">
-        <v>0.577865871177346</v>
-      </c>
-      <c r="AO46" s="0" t="s">
+      <c r="AO46" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW46" s="0" t="n">
-        <v>0.577865871177346</v>
+        <v>0.151733</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="1" t="n">
         <v>192</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="D47" s="1" t="n">
+      <c r="D47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="F47" s="1" t="n">
+      <c r="F47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="G47" s="1" t="n">
+      <c r="G47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="H47" s="1" t="n">
+      <c r="H47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="I47" s="1" t="n">
+      <c r="I47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="K47" s="0" t="n">
+      <c r="K47" s="1" t="n">
         <v>0.793457817503847</v>
       </c>
-      <c r="L47" s="0" t="n">
+      <c r="L47" s="1" t="n">
         <v>0.793457817503847</v>
       </c>
-      <c r="M47" s="0" t="n">
+      <c r="M47" s="1" t="n">
         <v>0.793457817503847</v>
       </c>
-      <c r="N47" s="0" t="n">
+      <c r="N47" s="1" t="n">
         <v>0.793457817503847</v>
       </c>
-      <c r="R47" s="0" t="n">
+      <c r="R47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S47" s="0" t="n">
+      <c r="S47" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T47" s="0" t="s">
+      <c r="T47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U47" s="1" t="n">
+      <c r="U47" s="2" t="n">
         <v>300.93262757379</v>
       </c>
-      <c r="V47" s="0" t="n">
+      <c r="V47" s="1" t="n">
         <v>0.588726282360253</v>
       </c>
-      <c r="W47" s="1" t="n">
-        <v>2782915886.74191</v>
-      </c>
-      <c r="X47" s="0" t="n">
+      <c r="W47" s="2" t="n">
+        <v>32205240</v>
+      </c>
+      <c r="X47" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y47" s="0" t="s">
+      <c r="Y47" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Z47" s="0" t="s">
+      <c r="Z47" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AA47" s="1" t="n">
+      <c r="AA47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
-      <c r="AB47" s="1" t="n">
+      <c r="AB47" s="2" t="n">
         <v>1774423157.79604</v>
       </c>
       <c r="AC47" s="0" t="n">
-        <v>0.736764039935823</v>
+        <v>0.170079</v>
       </c>
       <c r="AD47" s="0" t="n">
-        <v>0.736764039935823</v>
+        <v>0.170079</v>
       </c>
       <c r="AE47" s="0" t="n">
-        <v>0.736764039935823</v>
+        <v>0.170079</v>
       </c>
       <c r="AF47" s="0" t="n">
-        <v>0.736764039935823</v>
+        <v>0.170079</v>
       </c>
       <c r="AG47" s="0" t="n">
+        <v>0.170079</v>
+      </c>
+      <c r="AH47" s="0" t="n">
+        <v>0.170079</v>
+      </c>
+      <c r="AI47" s="1" t="n">
         <v>0.588726282360253</v>
       </c>
-      <c r="AH47" s="0" t="n">
+      <c r="AJ47" s="1" t="n">
         <v>0.588726282360253</v>
       </c>
-      <c r="AI47" s="0" t="n">
+      <c r="AK47" s="1" t="n">
         <v>0.588726282360253</v>
       </c>
-      <c r="AJ47" s="0" t="n">
+      <c r="AL47" s="1" t="n">
         <v>0.588726282360253</v>
       </c>
-      <c r="AK47" s="0" t="n">
-        <v>0.588726282360253</v>
-      </c>
-      <c r="AL47" s="0" t="n">
-        <v>0.588726282360253</v>
-      </c>
-      <c r="AO47" s="0" t="s">
+      <c r="AO47" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW47" s="0" t="n">
-        <v>0.588726282360253</v>
+        <v>0.170079</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="1" t="n">
         <v>193</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="D48" s="1" t="n">
+      <c r="D48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="F48" s="1" t="n">
+      <c r="F48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="G48" s="1" t="n">
+      <c r="G48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="H48" s="1" t="n">
+      <c r="H48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="I48" s="1" t="n">
+      <c r="I48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="K48" s="0" t="n">
+      <c r="K48" s="1" t="n">
         <v>0.807701972243676</v>
       </c>
-      <c r="L48" s="0" t="n">
+      <c r="L48" s="1" t="n">
         <v>0.807701972243676</v>
       </c>
-      <c r="M48" s="0" t="n">
+      <c r="M48" s="1" t="n">
         <v>0.807701972243676</v>
       </c>
-      <c r="N48" s="0" t="n">
+      <c r="N48" s="1" t="n">
         <v>0.807701972243676</v>
       </c>
-      <c r="R48" s="0" t="n">
+      <c r="R48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S48" s="0" t="n">
+      <c r="S48" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T48" s="0" t="s">
+      <c r="T48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U48" s="1" t="n">
+      <c r="U48" s="2" t="n">
         <v>312.906736824951</v>
       </c>
-      <c r="V48" s="0" t="n">
+      <c r="V48" s="1" t="n">
         <v>0.599790804110931</v>
       </c>
-      <c r="W48" s="1" t="n">
-        <v>2911217743.20557</v>
-      </c>
-      <c r="X48" s="0" t="n">
+      <c r="W48" s="2" t="n">
+        <v>44244325</v>
+      </c>
+      <c r="X48" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y48" s="0" t="s">
+      <c r="Y48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Z48" s="0" t="s">
+      <c r="Z48" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="AA48" s="1" t="n">
+      <c r="AA48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
-      <c r="AB48" s="1" t="n">
+      <c r="AB48" s="2" t="n">
         <v>1888907165.51389</v>
       </c>
       <c r="AC48" s="0" t="n">
-        <v>0.754279868221258</v>
+        <v>0.190643</v>
       </c>
       <c r="AD48" s="0" t="n">
-        <v>0.754279868221258</v>
+        <v>0.190643</v>
       </c>
       <c r="AE48" s="0" t="n">
-        <v>0.754279868221258</v>
+        <v>0.190643</v>
       </c>
       <c r="AF48" s="0" t="n">
-        <v>0.754279868221258</v>
+        <v>0.190643</v>
       </c>
       <c r="AG48" s="0" t="n">
+        <v>0.190643</v>
+      </c>
+      <c r="AH48" s="0" t="n">
+        <v>0.190643</v>
+      </c>
+      <c r="AI48" s="1" t="n">
         <v>0.599790804110931</v>
       </c>
-      <c r="AH48" s="0" t="n">
+      <c r="AJ48" s="1" t="n">
         <v>0.599790804110931</v>
       </c>
-      <c r="AI48" s="0" t="n">
+      <c r="AK48" s="1" t="n">
         <v>0.599790804110931</v>
       </c>
-      <c r="AJ48" s="0" t="n">
+      <c r="AL48" s="1" t="n">
         <v>0.599790804110931</v>
       </c>
-      <c r="AK48" s="0" t="n">
-        <v>0.599790804110931</v>
-      </c>
-      <c r="AL48" s="0" t="n">
-        <v>0.599790804110931</v>
-      </c>
-      <c r="AO48" s="0" t="s">
+      <c r="AO48" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW48" s="0" t="n">
-        <v>0.599790804110931</v>
+        <v>0.190643</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="1" t="n">
         <v>194</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="D49" s="1" t="n">
+      <c r="D49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="F49" s="1" t="n">
+      <c r="F49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="G49" s="1" t="n">
+      <c r="G49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="H49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="I49" s="1" t="n">
+      <c r="I49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="K49" s="0" t="n">
+      <c r="K49" s="1" t="n">
         <v>0.822201838049394</v>
       </c>
-      <c r="L49" s="0" t="n">
+      <c r="L49" s="1" t="n">
         <v>0.822201838049394</v>
       </c>
-      <c r="M49" s="0" t="n">
+      <c r="M49" s="1" t="n">
         <v>0.822201838049394</v>
       </c>
-      <c r="N49" s="0" t="n">
+      <c r="N49" s="1" t="n">
         <v>0.822201838049394</v>
       </c>
-      <c r="R49" s="0" t="n">
+      <c r="R49" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S49" s="0" t="n">
+      <c r="S49" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T49" s="0" t="s">
+      <c r="T49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U49" s="1" t="n">
+      <c r="U49" s="2" t="n">
         <v>325.357295883216</v>
       </c>
-      <c r="V49" s="0" t="n">
+      <c r="V49" s="1" t="n">
         <v>0.611063272483392</v>
       </c>
-      <c r="W49" s="1" t="n">
-        <v>3045434750.19549</v>
-      </c>
-      <c r="X49" s="0" t="n">
+      <c r="W49" s="2" t="n">
+        <v>60783906</v>
+      </c>
+      <c r="X49" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y49" s="0" t="s">
+      <c r="Y49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="Z49" s="0" t="s">
+      <c r="Z49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="AA49" s="1" t="n">
+      <c r="AA49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
-      <c r="AB49" s="1" t="n">
+      <c r="AB49" s="2" t="n">
         <v>2010777566.92568</v>
       </c>
       <c r="AC49" s="0" t="n">
-        <v>0.77221211780835</v>
+        <v>0.213693</v>
       </c>
       <c r="AD49" s="0" t="n">
-        <v>0.77221211780835</v>
+        <v>0.213693</v>
       </c>
       <c r="AE49" s="0" t="n">
-        <v>0.77221211780835</v>
+        <v>0.213693</v>
       </c>
       <c r="AF49" s="0" t="n">
-        <v>0.77221211780835</v>
+        <v>0.213693</v>
       </c>
       <c r="AG49" s="0" t="n">
+        <v>0.213693</v>
+      </c>
+      <c r="AH49" s="0" t="n">
+        <v>0.213693</v>
+      </c>
+      <c r="AI49" s="1" t="n">
         <v>0.611063272483392</v>
       </c>
-      <c r="AH49" s="0" t="n">
+      <c r="AJ49" s="1" t="n">
         <v>0.611063272483392</v>
       </c>
-      <c r="AI49" s="0" t="n">
+      <c r="AK49" s="1" t="n">
         <v>0.611063272483392</v>
       </c>
-      <c r="AJ49" s="0" t="n">
+      <c r="AL49" s="1" t="n">
         <v>0.611063272483392</v>
       </c>
-      <c r="AK49" s="0" t="n">
-        <v>0.611063272483392</v>
-      </c>
-      <c r="AL49" s="0" t="n">
-        <v>0.611063272483392</v>
-      </c>
-      <c r="AO49" s="0" t="s">
+      <c r="AO49" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW49" s="0" t="n">
-        <v>0.611063272483392</v>
+        <v>0.213693</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="1" t="n">
         <v>195</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="D50" s="1" t="n">
+      <c r="D50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="F50" s="1" t="n">
+      <c r="F50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="G50" s="1" t="n">
+      <c r="G50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="H50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="I50" s="1" t="n">
+      <c r="I50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="K50" s="0" t="n">
+      <c r="K50" s="1" t="n">
         <v>0.836962005446057</v>
       </c>
-      <c r="L50" s="0" t="n">
+      <c r="L50" s="1" t="n">
         <v>0.836962005446057</v>
       </c>
-      <c r="M50" s="0" t="n">
+      <c r="M50" s="1" t="n">
         <v>0.836962005446057</v>
       </c>
-      <c r="N50" s="0" t="n">
+      <c r="N50" s="1" t="n">
         <v>0.836962005446057</v>
       </c>
-      <c r="R50" s="0" t="n">
+      <c r="R50" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S50" s="0" t="n">
+      <c r="S50" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T50" s="0" t="s">
+      <c r="T50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U50" s="1" t="n">
+      <c r="U50" s="2" t="n">
         <v>338.303262686409</v>
       </c>
-      <c r="V50" s="0" t="n">
+      <c r="V50" s="1" t="n">
         <v>0.622547595626445</v>
       </c>
-      <c r="W50" s="1" t="n">
-        <v>3185839616.20331</v>
-      </c>
-      <c r="X50" s="0" t="n">
+      <c r="W50" s="2" t="n">
+        <v>83506376</v>
+      </c>
+      <c r="X50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y50" s="0" t="s">
+      <c r="Y50" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Z50" s="0" t="s">
+      <c r="Z50" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="AA50" s="1" t="n">
+      <c r="AA50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
-      <c r="AB50" s="1" t="n">
+      <c r="AB50" s="2" t="n">
         <v>2140510924.76615</v>
       </c>
       <c r="AC50" s="0" t="n">
-        <v>0.790570688697125</v>
+        <v>0.239531</v>
       </c>
       <c r="AD50" s="0" t="n">
-        <v>0.790570688697125</v>
+        <v>0.239531</v>
       </c>
       <c r="AE50" s="0" t="n">
-        <v>0.790570688697125</v>
+        <v>0.239531</v>
       </c>
       <c r="AF50" s="0" t="n">
-        <v>0.790570688697125</v>
+        <v>0.239531</v>
       </c>
       <c r="AG50" s="0" t="n">
+        <v>0.239531</v>
+      </c>
+      <c r="AH50" s="0" t="n">
+        <v>0.239531</v>
+      </c>
+      <c r="AI50" s="1" t="n">
         <v>0.622547595626445</v>
       </c>
-      <c r="AH50" s="0" t="n">
+      <c r="AJ50" s="1" t="n">
         <v>0.622547595626445</v>
       </c>
-      <c r="AI50" s="0" t="n">
+      <c r="AK50" s="1" t="n">
         <v>0.622547595626445</v>
       </c>
-      <c r="AJ50" s="0" t="n">
+      <c r="AL50" s="1" t="n">
         <v>0.622547595626445</v>
       </c>
-      <c r="AK50" s="0" t="n">
-        <v>0.622547595626445</v>
-      </c>
-      <c r="AL50" s="0" t="n">
-        <v>0.622547595626445</v>
-      </c>
-      <c r="AO50" s="0" t="s">
+      <c r="AO50" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW50" s="0" t="n">
-        <v>0.622547595626445</v>
+        <v>0.239531</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="1" t="n">
         <v>196</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="D51" s="1" t="n">
+      <c r="D51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="F51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="G51" s="1" t="n">
+      <c r="G51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="H51" s="1" t="n">
+      <c r="H51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="I51" s="1" t="n">
+      <c r="I51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="K51" s="0" t="n">
+      <c r="K51" s="1" t="n">
         <v>0.851987147367824</v>
       </c>
-      <c r="L51" s="0" t="n">
+      <c r="L51" s="1" t="n">
         <v>0.851987147367824</v>
       </c>
-      <c r="M51" s="0" t="n">
+      <c r="M51" s="1" t="n">
         <v>0.851987147367824</v>
       </c>
-      <c r="N51" s="0" t="n">
+      <c r="N51" s="1" t="n">
         <v>0.851987147367824</v>
       </c>
-      <c r="R51" s="0" t="n">
+      <c r="R51" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S51" s="0" t="n">
+      <c r="S51" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T51" s="0" t="s">
+      <c r="T51" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U51" s="1" t="n">
+      <c r="U51" s="2" t="n">
         <v>351.764349508701</v>
       </c>
-      <c r="V51" s="0" t="n">
+      <c r="V51" s="1" t="n">
         <v>0.634247755138648</v>
       </c>
-      <c r="W51" s="1" t="n">
-        <v>3332717622.50658</v>
-      </c>
-      <c r="X51" s="0" t="n">
+      <c r="W51" s="2" t="n">
+        <v>114723047</v>
+      </c>
+      <c r="X51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y51" s="0" t="s">
+      <c r="Y51" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="Z51" s="0" t="s">
+      <c r="Z51" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="AA51" s="1" t="n">
+      <c r="AA51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
-      <c r="AB51" s="1" t="n">
+      <c r="AB51" s="2" t="n">
         <v>2278614549.12114</v>
       </c>
       <c r="AC51" s="0" t="n">
-        <v>0.809365716250211</v>
+        <v>0.268492</v>
       </c>
       <c r="AD51" s="0" t="n">
-        <v>0.809365716250211</v>
+        <v>0.268492</v>
       </c>
       <c r="AE51" s="0" t="n">
-        <v>0.809365716250211</v>
+        <v>0.268492</v>
       </c>
       <c r="AF51" s="0" t="n">
-        <v>0.809365716250211</v>
+        <v>0.268492</v>
       </c>
       <c r="AG51" s="0" t="n">
+        <v>0.268492</v>
+      </c>
+      <c r="AH51" s="0" t="n">
+        <v>0.268492</v>
+      </c>
+      <c r="AI51" s="1" t="n">
         <v>0.634247755138648</v>
       </c>
-      <c r="AH51" s="0" t="n">
+      <c r="AJ51" s="1" t="n">
         <v>0.634247755138648</v>
       </c>
-      <c r="AI51" s="0" t="n">
+      <c r="AK51" s="1" t="n">
         <v>0.634247755138648</v>
       </c>
-      <c r="AJ51" s="0" t="n">
+      <c r="AL51" s="1" t="n">
         <v>0.634247755138648</v>
       </c>
-      <c r="AK51" s="0" t="n">
-        <v>0.634247755138648</v>
-      </c>
-      <c r="AL51" s="0" t="n">
-        <v>0.634247755138648</v>
-      </c>
-      <c r="AO51" s="0" t="s">
+      <c r="AO51" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW51" s="0" t="n">
-        <v>0.634247755138648</v>
+        <v>0.268492</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="1" t="n">
         <v>197</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="D52" s="1" t="n">
+      <c r="D52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="F52" s="1" t="n">
+      <c r="F52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="G52" s="1" t="n">
+      <c r="G52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="H52" s="1" t="n">
+      <c r="H52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="I52" s="1" t="n">
+      <c r="I52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="K52" s="0" t="n">
+      <c r="K52" s="1" t="n">
         <v>0.867282020637372</v>
       </c>
-      <c r="L52" s="0" t="n">
+      <c r="L52" s="1" t="n">
         <v>0.867282020637372</v>
       </c>
-      <c r="M52" s="0" t="n">
+      <c r="M52" s="1" t="n">
         <v>0.867282020637372</v>
       </c>
-      <c r="N52" s="0" t="n">
+      <c r="N52" s="1" t="n">
         <v>0.867282020637372</v>
       </c>
-      <c r="R52" s="0" t="n">
+      <c r="R52" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S52" s="0" t="n">
+      <c r="S52" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T52" s="0" t="s">
+      <c r="T52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U52" s="1" t="n">
+      <c r="U52" s="2" t="n">
         <v>365.761052975653</v>
       </c>
-      <c r="V52" s="0" t="n">
+      <c r="V52" s="1" t="n">
         <v>0.646167807448724</v>
       </c>
-      <c r="W52" s="1" t="n">
-        <v>3486367202.81688</v>
-      </c>
-      <c r="X52" s="0" t="n">
+      <c r="W52" s="2" t="n">
+        <v>157609251</v>
+      </c>
+      <c r="X52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" s="0" t="s">
+      <c r="Y52" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Z52" s="0" t="s">
+      <c r="Z52" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="AA52" s="1" t="n">
+      <c r="AA52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
-      <c r="AB52" s="1" t="n">
+      <c r="AB52" s="2" t="n">
         <v>2425628481.21589</v>
       </c>
       <c r="AC52" s="0" t="n">
-        <v>0.828607576788343</v>
+        <v>0.300955</v>
       </c>
       <c r="AD52" s="0" t="n">
-        <v>0.828607576788343</v>
+        <v>0.300955</v>
       </c>
       <c r="AE52" s="0" t="n">
-        <v>0.828607576788343</v>
+        <v>0.300955</v>
       </c>
       <c r="AF52" s="0" t="n">
-        <v>0.828607576788343</v>
+        <v>0.300955</v>
       </c>
       <c r="AG52" s="0" t="n">
+        <v>0.300955</v>
+      </c>
+      <c r="AH52" s="0" t="n">
+        <v>0.300955</v>
+      </c>
+      <c r="AI52" s="1" t="n">
         <v>0.646167807448724</v>
       </c>
-      <c r="AH52" s="0" t="n">
+      <c r="AJ52" s="1" t="n">
         <v>0.646167807448724</v>
       </c>
-      <c r="AI52" s="0" t="n">
+      <c r="AK52" s="1" t="n">
         <v>0.646167807448724</v>
       </c>
-      <c r="AJ52" s="0" t="n">
+      <c r="AL52" s="1" t="n">
         <v>0.646167807448724</v>
       </c>
-      <c r="AK52" s="0" t="n">
-        <v>0.646167807448724</v>
-      </c>
-      <c r="AL52" s="0" t="n">
-        <v>0.646167807448724</v>
-      </c>
-      <c r="AO52" s="0" t="s">
+      <c r="AO52" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW52" s="0" t="n">
-        <v>0.646167807448724</v>
+        <v>0.300955</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="1" t="n">
         <v>198</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="D53" s="1" t="n">
+      <c r="D53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="G53" s="1" t="n">
+      <c r="G53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="H53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="I53" s="1" t="n">
+      <c r="I53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="K53" s="0" t="n">
+      <c r="K53" s="1" t="n">
         <v>0.882851467471854</v>
       </c>
-      <c r="L53" s="0" t="n">
+      <c r="L53" s="1" t="n">
         <v>0.882851467471854</v>
       </c>
-      <c r="M53" s="0" t="n">
+      <c r="M53" s="1" t="n">
         <v>0.882851467471854</v>
       </c>
-      <c r="N53" s="0" t="n">
+      <c r="N53" s="1" t="n">
         <v>0.882851467471854</v>
       </c>
-      <c r="R53" s="0" t="n">
+      <c r="R53" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S53" s="0" t="n">
+      <c r="S53" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T53" s="0" t="s">
+      <c r="T53" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U53" s="1" t="n">
+      <c r="U53" s="2" t="n">
         <v>380.314685273554</v>
       </c>
-      <c r="V53" s="0" t="n">
+      <c r="V53" s="1" t="n">
         <v>0.658311885221915</v>
       </c>
-      <c r="W53" s="1" t="n">
-        <v>3647100549.65155</v>
-      </c>
-      <c r="X53" s="0" t="n">
+      <c r="W53" s="2" t="n">
+        <v>216527340</v>
+      </c>
+      <c r="X53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y53" s="0" t="s">
+      <c r="Y53" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="Z53" s="0" t="s">
+      <c r="Z53" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AA53" s="1" t="n">
+      <c r="AA53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
-      <c r="AB53" s="1" t="n">
+      <c r="AB53" s="2" t="n">
         <v>2582127605.19546</v>
       </c>
       <c r="AC53" s="0" t="n">
-        <v>0.848306893318909</v>
+        <v>0.337343</v>
       </c>
       <c r="AD53" s="0" t="n">
-        <v>0.848306893318909</v>
+        <v>0.337343</v>
       </c>
       <c r="AE53" s="0" t="n">
-        <v>0.848306893318909</v>
+        <v>0.337343</v>
       </c>
       <c r="AF53" s="0" t="n">
-        <v>0.848306893318909</v>
+        <v>0.337343</v>
       </c>
       <c r="AG53" s="0" t="n">
+        <v>0.337343</v>
+      </c>
+      <c r="AH53" s="0" t="n">
+        <v>0.337343</v>
+      </c>
+      <c r="AI53" s="1" t="n">
         <v>0.658311885221915</v>
       </c>
-      <c r="AH53" s="0" t="n">
+      <c r="AJ53" s="1" t="n">
         <v>0.658311885221915</v>
       </c>
-      <c r="AI53" s="0" t="n">
+      <c r="AK53" s="1" t="n">
         <v>0.658311885221915</v>
       </c>
-      <c r="AJ53" s="0" t="n">
+      <c r="AL53" s="1" t="n">
         <v>0.658311885221915</v>
       </c>
-      <c r="AK53" s="0" t="n">
-        <v>0.658311885221915</v>
-      </c>
-      <c r="AL53" s="0" t="n">
-        <v>0.658311885221915</v>
-      </c>
-      <c r="AO53" s="0" t="s">
+      <c r="AO53" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW53" s="0" t="n">
-        <v>0.658311885221915</v>
+        <v>0.337343</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="1" t="n">
         <v>199</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="D54" s="1" t="n">
+      <c r="D54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="F54" s="1" t="n">
+      <c r="F54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="G54" s="1" t="n">
+      <c r="G54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="H54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="I54" s="1" t="n">
+      <c r="I54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="K54" s="0" t="n">
+      <c r="K54" s="1" t="n">
         <v>0.898700417015908</v>
       </c>
-      <c r="L54" s="0" t="n">
+      <c r="L54" s="1" t="n">
         <v>0.898700417015908</v>
       </c>
-      <c r="M54" s="0" t="n">
+      <c r="M54" s="1" t="n">
         <v>0.898700417015908</v>
       </c>
-      <c r="N54" s="0" t="n">
+      <c r="N54" s="1" t="n">
         <v>0.898700417015908</v>
       </c>
-      <c r="R54" s="0" t="n">
+      <c r="R54" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S54" s="0" t="n">
+      <c r="S54" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T54" s="0" t="s">
+      <c r="T54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U54" s="1" t="n">
+      <c r="U54" s="2" t="n">
         <v>395.447406600589</v>
       </c>
-      <c r="V54" s="0" t="n">
+      <c r="V54" s="1" t="n">
         <v>0.670684198792776</v>
       </c>
-      <c r="W54" s="1" t="n">
-        <v>3815244248.66135</v>
-      </c>
-      <c r="X54" s="0" t="n">
+      <c r="W54" s="2" t="n">
+        <v>297470412</v>
+      </c>
+      <c r="X54" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y54" s="0" t="s">
+      <c r="Y54" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Z54" s="0" t="s">
+      <c r="Z54" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AA54" s="1" t="n">
+      <c r="AA54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
-      <c r="AB54" s="1" t="n">
+      <c r="AB54" s="2" t="n">
         <v>2748723896.15506</v>
       </c>
       <c r="AC54" s="0" t="n">
-        <v>0.868474541400673</v>
+        <v>0.37813</v>
       </c>
       <c r="AD54" s="0" t="n">
-        <v>0.868474541400673</v>
+        <v>0.37813</v>
       </c>
       <c r="AE54" s="0" t="n">
-        <v>0.868474541400673</v>
+        <v>0.37813</v>
       </c>
       <c r="AF54" s="0" t="n">
-        <v>0.868474541400673</v>
+        <v>0.37813</v>
       </c>
       <c r="AG54" s="0" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="AH54" s="0" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="AI54" s="1" t="n">
         <v>0.670684198792776</v>
       </c>
-      <c r="AH54" s="0" t="n">
+      <c r="AJ54" s="1" t="n">
         <v>0.670684198792776</v>
       </c>
-      <c r="AI54" s="0" t="n">
+      <c r="AK54" s="1" t="n">
         <v>0.670684198792776</v>
       </c>
-      <c r="AJ54" s="0" t="n">
+      <c r="AL54" s="1" t="n">
         <v>0.670684198792776</v>
       </c>
-      <c r="AK54" s="0" t="n">
-        <v>0.670684198792776</v>
-      </c>
-      <c r="AL54" s="0" t="n">
-        <v>0.670684198792776</v>
-      </c>
-      <c r="AO54" s="0" t="s">
+      <c r="AO54" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW54" s="0" t="n">
-        <v>0.670684198792776</v>
+        <v>0.37813</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="D55" s="1" t="n">
+      <c r="D55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="G55" s="1" t="n">
+      <c r="G55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="H55" s="1" t="n">
+      <c r="H55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="I55" s="1" t="n">
+      <c r="I55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="K55" s="0" t="n">
+      <c r="K55" s="1" t="n">
         <v>0.914833886902178</v>
       </c>
-      <c r="L55" s="0" t="n">
+      <c r="L55" s="1" t="n">
         <v>0.914833886902178</v>
       </c>
-      <c r="M55" s="0" t="n">
+      <c r="M55" s="1" t="n">
         <v>0.914833886902178</v>
       </c>
-      <c r="N55" s="0" t="n">
+      <c r="N55" s="1" t="n">
         <v>0.914833886902178</v>
       </c>
-      <c r="R55" s="0" t="n">
+      <c r="R55" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S55" s="0" t="n">
+      <c r="S55" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T55" s="0" t="s">
+      <c r="T55" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U55" s="1" t="n">
+      <c r="U55" s="2" t="n">
         <v>411.182258909226</v>
       </c>
-      <c r="V55" s="0" t="n">
+      <c r="V55" s="1" t="n">
         <v>0.683289037624888</v>
       </c>
-      <c r="W55" s="1" t="n">
-        <v>3991139942.20264</v>
-      </c>
-      <c r="X55" s="0" t="n">
+      <c r="W55" s="2" t="n">
+        <v>408671930</v>
+      </c>
+      <c r="X55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y55" s="0" t="s">
+      <c r="Y55" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Z55" s="0" t="s">
+      <c r="Z55" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AA55" s="1" t="n">
+      <c r="AA55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
-      <c r="AB55" s="1" t="n">
+      <c r="AB55" s="2" t="n">
         <v>2926068813.21109</v>
       </c>
       <c r="AC55" s="0" t="n">
-        <v>0.889121655147933</v>
+        <v>0.423849</v>
       </c>
       <c r="AD55" s="0" t="n">
-        <v>0.889121655147933</v>
+        <v>0.423849</v>
       </c>
       <c r="AE55" s="0" t="n">
-        <v>0.889121655147933</v>
+        <v>0.423849</v>
       </c>
       <c r="AF55" s="0" t="n">
-        <v>0.889121655147933</v>
+        <v>0.423849</v>
       </c>
       <c r="AG55" s="0" t="n">
+        <v>0.423849</v>
+      </c>
+      <c r="AH55" s="0" t="n">
+        <v>0.423849</v>
+      </c>
+      <c r="AI55" s="1" t="n">
         <v>0.683289037624888</v>
       </c>
-      <c r="AH55" s="0" t="n">
+      <c r="AJ55" s="1" t="n">
         <v>0.683289037624888</v>
       </c>
-      <c r="AI55" s="0" t="n">
+      <c r="AK55" s="1" t="n">
         <v>0.683289037624888</v>
       </c>
-      <c r="AJ55" s="0" t="n">
+      <c r="AL55" s="1" t="n">
         <v>0.683289037624888</v>
       </c>
-      <c r="AK55" s="0" t="n">
-        <v>0.683289037624888</v>
-      </c>
-      <c r="AL55" s="0" t="n">
-        <v>0.683289037624888</v>
-      </c>
-      <c r="AO55" s="0" t="s">
+      <c r="AO55" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW55" s="0" t="n">
-        <v>0.683289037624888</v>
+        <v>0.423849</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="D56" s="1" t="n">
+      <c r="D56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="F56" s="1" t="n">
+      <c r="F56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="G56" s="1" t="n">
+      <c r="G56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="I56" s="1" t="n">
+      <c r="I56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="K56" s="0" t="n">
+      <c r="K56" s="1" t="n">
         <v>0.931256984839846</v>
       </c>
-      <c r="L56" s="0" t="n">
+      <c r="L56" s="1" t="n">
         <v>0.931256984839846</v>
       </c>
-      <c r="M56" s="0" t="n">
+      <c r="M56" s="1" t="n">
         <v>0.931256984839846</v>
       </c>
-      <c r="N56" s="0" t="n">
+      <c r="N56" s="1" t="n">
         <v>0.931256984839846</v>
       </c>
-      <c r="R56" s="0" t="n">
+      <c r="R56" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S56" s="0" t="n">
+      <c r="S56" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T56" s="0" t="s">
+      <c r="T56" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U56" s="1" t="n">
+      <c r="U56" s="2" t="n">
         <v>427.543200991224</v>
       </c>
-      <c r="V56" s="0" t="n">
+      <c r="V56" s="1" t="n">
         <v>0.69613077179801</v>
       </c>
-      <c r="W56" s="1" t="n">
-        <v>4175145023.50259</v>
-      </c>
-      <c r="X56" s="0" t="n">
+      <c r="W56" s="2" t="n">
+        <v>561443221</v>
+      </c>
+      <c r="X56" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y56" s="0" t="s">
+      <c r="Y56" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="Z56" s="0" t="s">
+      <c r="Z56" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AA56" s="1" t="n">
+      <c r="AA56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
-      <c r="AB56" s="1" t="n">
+      <c r="AB56" s="2" t="n">
         <v>3114855846.97066</v>
       </c>
       <c r="AC56" s="0" t="n">
-        <v>0.91025963337742</v>
+        <v>0.475096</v>
       </c>
       <c r="AD56" s="0" t="n">
-        <v>0.91025963337742</v>
+        <v>0.475096</v>
       </c>
       <c r="AE56" s="0" t="n">
-        <v>0.91025963337742</v>
+        <v>0.475096</v>
       </c>
       <c r="AF56" s="0" t="n">
-        <v>0.91025963337742</v>
+        <v>0.475096</v>
       </c>
       <c r="AG56" s="0" t="n">
+        <v>0.475096</v>
+      </c>
+      <c r="AH56" s="0" t="n">
+        <v>0.475096</v>
+      </c>
+      <c r="AI56" s="1" t="n">
         <v>0.69613077179801</v>
       </c>
-      <c r="AH56" s="0" t="n">
+      <c r="AJ56" s="1" t="n">
         <v>0.69613077179801</v>
       </c>
-      <c r="AI56" s="0" t="n">
+      <c r="AK56" s="1" t="n">
         <v>0.69613077179801</v>
       </c>
-      <c r="AJ56" s="0" t="n">
+      <c r="AL56" s="1" t="n">
         <v>0.69613077179801</v>
       </c>
-      <c r="AK56" s="0" t="n">
-        <v>0.69613077179801</v>
-      </c>
-      <c r="AL56" s="0" t="n">
-        <v>0.69613077179801</v>
-      </c>
-      <c r="AO56" s="0" t="s">
+      <c r="AO56" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW56" s="0" t="n">
-        <v>0.69613077179801</v>
+        <v>0.475096</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="1" t="n">
         <v>202</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="D57" s="1" t="n">
+      <c r="D57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="F57" s="1" t="n">
+      <c r="F57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="G57" s="1" t="n">
+      <c r="G57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="H57" s="1" t="n">
+      <c r="H57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="I57" s="1" t="n">
+      <c r="I57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="K57" s="0" t="n">
+      <c r="K57" s="1" t="n">
         <v>0.947974910231691</v>
       </c>
-      <c r="L57" s="0" t="n">
+      <c r="L57" s="1" t="n">
         <v>0.947974910231691</v>
       </c>
-      <c r="M57" s="0" t="n">
+      <c r="M57" s="1" t="n">
         <v>0.947974910231691</v>
       </c>
-      <c r="N57" s="0" t="n">
+      <c r="N57" s="1" t="n">
         <v>0.947974910231691</v>
       </c>
-      <c r="R57" s="0" t="n">
+      <c r="R57" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S57" s="0" t="n">
+      <c r="S57" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T57" s="0" t="s">
+      <c r="T57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U57" s="1" t="n">
+      <c r="U57" s="2" t="n">
         <v>444.555144958665</v>
       </c>
-      <c r="V57" s="0" t="n">
+      <c r="V57" s="1" t="n">
         <v>0.709213853523181</v>
       </c>
-      <c r="W57" s="1" t="n">
-        <v>4367633362.82769</v>
-      </c>
-      <c r="X57" s="0" t="n">
+      <c r="W57" s="2" t="n">
+        <v>771324057</v>
+      </c>
+      <c r="X57" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y57" s="0" t="s">
+      <c r="Y57" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="Z57" s="0" t="s">
+      <c r="Z57" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="AA57" s="1" t="n">
+      <c r="AA57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
-      <c r="AB57" s="1" t="n">
+      <c r="AB57" s="2" t="n">
         <v>3315823231.36136</v>
       </c>
       <c r="AC57" s="0" t="n">
-        <v>0.931900145901334</v>
+        <v>0.532539</v>
       </c>
       <c r="AD57" s="0" t="n">
-        <v>0.931900145901334</v>
+        <v>0.532539</v>
       </c>
       <c r="AE57" s="0" t="n">
-        <v>0.931900145901334</v>
+        <v>0.532539</v>
       </c>
       <c r="AF57" s="0" t="n">
-        <v>0.931900145901334</v>
+        <v>0.532539</v>
       </c>
       <c r="AG57" s="0" t="n">
+        <v>0.532539</v>
+      </c>
+      <c r="AH57" s="0" t="n">
+        <v>0.532539</v>
+      </c>
+      <c r="AI57" s="1" t="n">
         <v>0.709213853523181</v>
       </c>
-      <c r="AH57" s="0" t="n">
+      <c r="AJ57" s="1" t="n">
         <v>0.709213853523181</v>
       </c>
-      <c r="AI57" s="0" t="n">
+      <c r="AK57" s="1" t="n">
         <v>0.709213853523181</v>
       </c>
-      <c r="AJ57" s="0" t="n">
+      <c r="AL57" s="1" t="n">
         <v>0.709213853523181</v>
       </c>
-      <c r="AK57" s="0" t="n">
-        <v>0.709213853523181</v>
-      </c>
-      <c r="AL57" s="0" t="n">
-        <v>0.709213853523181</v>
-      </c>
-      <c r="AO57" s="0" t="s">
+      <c r="AO57" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW57" s="0" t="n">
-        <v>0.709213853523181</v>
+        <v>0.532539</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
+      <c r="A58" s="1" t="n">
         <v>203</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="D58" s="1" t="n">
+      <c r="D58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="F58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="G58" s="1" t="n">
+      <c r="G58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="H58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="I58" s="1" t="n">
+      <c r="I58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="K58" s="0" t="n">
+      <c r="K58" s="1" t="n">
         <v>0.96499295582017</v>
       </c>
-      <c r="L58" s="0" t="n">
+      <c r="L58" s="1" t="n">
         <v>0.96499295582017</v>
       </c>
-      <c r="M58" s="0" t="n">
+      <c r="M58" s="1" t="n">
         <v>0.96499295582017</v>
       </c>
-      <c r="N58" s="0" t="n">
+      <c r="N58" s="1" t="n">
         <v>0.96499295582017</v>
       </c>
-      <c r="R58" s="0" t="n">
+      <c r="R58" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S58" s="0" t="n">
+      <c r="S58" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T58" s="0" t="s">
+      <c r="T58" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U58" s="1" t="n">
+      <c r="U58" s="2" t="n">
         <v>462.24399417657</v>
       </c>
-      <c r="V58" s="0" t="n">
+      <c r="V58" s="1" t="n">
         <v>0.722542818686296</v>
       </c>
-      <c r="W58" s="1" t="n">
-        <v>4568996067.13115</v>
-      </c>
-      <c r="X58" s="0" t="n">
+      <c r="W58" s="2" t="n">
+        <v>1059663343</v>
+      </c>
+      <c r="X58" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y58" s="0" t="s">
+      <c r="Y58" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="Z58" s="0" t="s">
+      <c r="Z58" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AA58" s="1" t="n">
+      <c r="AA58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
-      <c r="AB58" s="1" t="n">
+      <c r="AB58" s="2" t="n">
         <v>3529756830.42556</v>
       </c>
       <c r="AC58" s="0" t="n">
-        <v>0.954055139969993</v>
+        <v>0.596927</v>
       </c>
       <c r="AD58" s="0" t="n">
-        <v>0.954055139969993</v>
+        <v>0.596927</v>
       </c>
       <c r="AE58" s="0" t="n">
-        <v>0.954055139969993</v>
+        <v>0.596927</v>
       </c>
       <c r="AF58" s="0" t="n">
-        <v>0.954055139969993</v>
+        <v>0.596927</v>
       </c>
       <c r="AG58" s="0" t="n">
+        <v>0.596927</v>
+      </c>
+      <c r="AH58" s="0" t="n">
+        <v>0.596927</v>
+      </c>
+      <c r="AI58" s="1" t="n">
         <v>0.722542818686296</v>
       </c>
-      <c r="AH58" s="0" t="n">
+      <c r="AJ58" s="1" t="n">
         <v>0.722542818686296</v>
       </c>
-      <c r="AI58" s="0" t="n">
+      <c r="AK58" s="1" t="n">
         <v>0.722542818686296</v>
       </c>
-      <c r="AJ58" s="0" t="n">
+      <c r="AL58" s="1" t="n">
         <v>0.722542818686296</v>
       </c>
-      <c r="AK58" s="0" t="n">
-        <v>0.722542818686296</v>
-      </c>
-      <c r="AL58" s="0" t="n">
-        <v>0.722542818686296</v>
-      </c>
-      <c r="AO58" s="0" t="s">
+      <c r="AO58" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW58" s="0" t="n">
-        <v>0.722542818686296</v>
+        <v>0.596927</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+      <c r="A59" s="1" t="n">
         <v>204</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="D59" s="1" t="n">
+      <c r="D59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="F59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="G59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="H59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="I59" s="1" t="n">
+      <c r="I59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="K59" s="0" t="n">
+      <c r="K59" s="1" t="n">
         <v>0.982316509363054</v>
       </c>
-      <c r="L59" s="0" t="n">
+      <c r="L59" s="1" t="n">
         <v>0.982316509363054</v>
       </c>
-      <c r="M59" s="0" t="n">
+      <c r="M59" s="1" t="n">
         <v>0.982316509363054</v>
       </c>
-      <c r="N59" s="0" t="n">
+      <c r="N59" s="1" t="n">
         <v>0.982316509363054</v>
       </c>
-      <c r="R59" s="0" t="n">
+      <c r="R59" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S59" s="0" t="n">
+      <c r="S59" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T59" s="0" t="s">
+      <c r="T59" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U59" s="1" t="n">
+      <c r="U59" s="2" t="n">
         <v>480.636682704856</v>
       </c>
-      <c r="V59" s="0" t="n">
+      <c r="V59" s="1" t="n">
         <v>0.736122288420686</v>
       </c>
-      <c r="W59" s="1" t="n">
-        <v>4779642274.72256</v>
-      </c>
-      <c r="X59" s="0" t="n">
+      <c r="W59" s="2" t="n">
+        <v>1455790715</v>
+      </c>
+      <c r="X59" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y59" s="0" t="s">
+      <c r="Y59" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="Z59" s="0" t="s">
+      <c r="Z59" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="AA59" s="1" t="n">
+      <c r="AA59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
-      <c r="AB59" s="1" t="n">
+      <c r="AB59" s="2" t="n">
         <v>3757493211.36779</v>
       </c>
       <c r="AC59" s="0" t="n">
-        <v>0.976736846867639</v>
+        <v>0.6691</v>
       </c>
       <c r="AD59" s="0" t="n">
-        <v>0.976736846867639</v>
+        <v>0.6691</v>
       </c>
       <c r="AE59" s="0" t="n">
-        <v>0.976736846867639</v>
+        <v>0.6691</v>
       </c>
       <c r="AF59" s="0" t="n">
-        <v>0.976736846867639</v>
+        <v>0.6691</v>
       </c>
       <c r="AG59" s="0" t="n">
+        <v>0.6691</v>
+      </c>
+      <c r="AH59" s="0" t="n">
+        <v>0.6691</v>
+      </c>
+      <c r="AI59" s="1" t="n">
         <v>0.736122288420686</v>
       </c>
-      <c r="AH59" s="0" t="n">
+      <c r="AJ59" s="1" t="n">
         <v>0.736122288420686</v>
       </c>
-      <c r="AI59" s="0" t="n">
+      <c r="AK59" s="1" t="n">
         <v>0.736122288420686</v>
       </c>
-      <c r="AJ59" s="0" t="n">
+      <c r="AL59" s="1" t="n">
         <v>0.736122288420686</v>
       </c>
-      <c r="AK59" s="0" t="n">
-        <v>0.736122288420686</v>
-      </c>
-      <c r="AL59" s="0" t="n">
-        <v>0.736122288420686</v>
-      </c>
-      <c r="AO59" s="0" t="s">
+      <c r="AO59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW59" s="0" t="n">
-        <v>0.736122288420686</v>
+        <v>0.6691</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+      <c r="A60" s="1" t="n">
         <v>205</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="D60" s="1" t="n">
+      <c r="D60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="F60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="G60" s="1" t="n">
+      <c r="G60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="H60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="I60" s="1" t="n">
+      <c r="I60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="K60" s="0" t="n">
+      <c r="K60" s="1" t="n">
         <v>0.999951055339139</v>
       </c>
-      <c r="L60" s="0" t="n">
+      <c r="L60" s="1" t="n">
         <v>0.999951055339139</v>
       </c>
-      <c r="M60" s="0" t="n">
+      <c r="M60" s="1" t="n">
         <v>0.999951055339139</v>
       </c>
-      <c r="N60" s="0" t="n">
+      <c r="N60" s="1" t="n">
         <v>0.999951055339139</v>
       </c>
-      <c r="R60" s="0" t="n">
+      <c r="R60" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S60" s="0" t="n">
+      <c r="S60" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T60" s="0" t="s">
+      <c r="T60" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U60" s="1" t="n">
+      <c r="U60" s="2" t="n">
         <v>499.761216309682</v>
       </c>
-      <c r="V60" s="0" t="n">
+      <c r="V60" s="1" t="n">
         <v>0.749956970709265</v>
       </c>
-      <c r="W60" s="1" t="n">
-        <v>5000000000</v>
-      </c>
-      <c r="X60" s="0" t="n">
+      <c r="W60" s="2" t="n">
+        <v>1999999925</v>
+      </c>
+      <c r="X60" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="Y60" s="0" t="s">
+      <c r="Y60" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="Z60" s="0" t="s">
+      <c r="Z60" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="AA60" s="1" t="n">
+      <c r="AA60" s="2" t="n">
         <v>4000000000</v>
       </c>
-      <c r="AB60" s="1" t="n">
+      <c r="AB60" s="2" t="n">
         <v>4000000000</v>
       </c>
       <c r="AC60" s="0" t="n">
-        <v>0.99995778866507</v>
+        <v>0.75</v>
       </c>
       <c r="AD60" s="0" t="n">
-        <v>0.99995778866507</v>
+        <v>0.75</v>
       </c>
       <c r="AE60" s="0" t="n">
-        <v>0.99995778866507</v>
+        <v>0.75</v>
       </c>
       <c r="AF60" s="0" t="n">
-        <v>0.99995778866507</v>
+        <v>0.75</v>
       </c>
       <c r="AG60" s="0" t="n">
         <v>0.75</v>
@@ -7620,19 +7625,19 @@
       <c r="AH60" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="AI60" s="0" t="n">
+      <c r="AI60" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="AJ60" s="0" t="n">
+      <c r="AJ60" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="AK60" s="0" t="n">
+      <c r="AK60" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="AL60" s="0" t="n">
+      <c r="AL60" s="1" t="n">
         <v>0.75</v>
       </c>
-      <c r="AO60" s="0" t="s">
+      <c r="AO60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AW60" s="0" t="n">
